--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -77,7 +77,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -283,7 +283,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -489,7 +489,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -695,7 +695,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -901,7 +901,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -1125,19 +1125,19 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Date Worked 1 (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
   </si>
   <si>
     <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected.</t>
   </si>
   <si>
-    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
-  </si>
-  <si>
-    <t>Processed Date and Date Worked 1</t>
-  </si>
-  <si>
-    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Date Worked 1 starts empty.</t>
+    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
+  </si>
+  <si>
+    <t>Processed Date and Latest Date Worked</t>
+  </si>
+  <si>
+    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Latest Date Worked starts empty.</t>
   </si>
   <si>
     <t>Processed Date is filled in wherever the row had something to fill it with: the date written into the Notes where there was one, otherwise the Insurance Check Date. A date from the Notes is never overwritten by a check date. Where the row has neither, it is blank for you to fill in.</t>
@@ -1197,7 +1197,7 @@
     <t>Procedure Code</t>
   </si>
   <si>
-    <t>Date Worked 1</t>
+    <t>Latest Date Worked</t>
   </si>
   <si>
     <t>Days Until Deadline</t>
@@ -5778,11 +5778,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="H16" t="s">
-        <v>151</v>
-      </c>
-    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:AO12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="L2:L12">

--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">BH!$A$1:$AO$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DME!$A$1:$AO$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">GAE!$A$1:$AO$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ORTHO!$A$1:$AO$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">US!$A$1:$AO$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DME!$A$1:$AO$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">GAE!$A$1:$AO$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ORTHO!$A$1:$AO$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">US!$A$1:$AO$20</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -5861,7 +5861,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AO34"/>
+  <dimension ref="A1:AO32"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6062,11 +6062,11 @@
         <v>46245</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L34" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>-23</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M14" ca="1" si="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
         <v>252</v>
       </c>
       <c r="N2" s="12">
@@ -6182,15 +6182,15 @@
         <v>46283</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>196</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
         <v>209</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" ref="N3:N14" ca="1" si="2">IF($C3="","",$C3+120-TODAY())</f>
+        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
         <v>-36</v>
       </c>
       <c r="O3" s="6">
@@ -6302,15 +6302,15 @@
         <v>46283</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>203</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
         <v>331</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
         <v>86</v>
       </c>
       <c r="O4" s="6">
@@ -6416,15 +6416,15 @@
         <v>46283</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>207</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
         <v>221</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
         <v>-24</v>
       </c>
       <c r="O5" s="6">
@@ -6532,15 +6532,15 @@
         <v>46283</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>207</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
         <v>329</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
         <v>84</v>
       </c>
       <c r="O6" s="6">
@@ -6648,15 +6648,15 @@
         <v>46261</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>207</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
         <v>233</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
         <v>-12</v>
       </c>
       <c r="O7" s="6">
@@ -6764,15 +6764,15 @@
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>208</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
         <v>230</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
         <v>-15</v>
       </c>
       <c r="O8" s="6">
@@ -6880,15 +6880,15 @@
         <v>46283</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
         <v>214</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
         <v>363</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
         <v>118</v>
       </c>
       <c r="O9" s="6">
@@ -6996,15 +6996,15 @@
         <v>46283</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
         <v>214</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
         <v>281</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
         <v>36</v>
       </c>
       <c r="O10" s="6">
@@ -7112,15 +7112,15 @@
         <v>46278</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
         <v>221</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
         <v>224</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
         <v>-21</v>
       </c>
       <c r="O11" s="6">
@@ -7197,50 +7197,46 @@
       <c r="A12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>523</v>
-      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="3">
-        <v>46206</v>
+        <v>46202</v>
       </c>
       <c r="D12" s="4">
-        <v>558717492</v>
+        <v>557798679</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="F12" s="6">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>162</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="K12" s="3">
-        <v>46261</v>
-      </c>
+      <c r="K12" s="3"/>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>222</v>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
+        <v>224</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>288</v>
+        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <v>284</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>43</v>
+        <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
+        <v>39</v>
       </c>
       <c r="O12" s="6">
-        <v>46505</v>
+        <v>46507</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>76</v>
@@ -7272,32 +7268,36 @@
         <v>6392.96</v>
       </c>
       <c r="AA12" s="7">
-        <v>0</v>
+        <v>5624.17</v>
       </c>
       <c r="AB12" s="7">
-        <v>174.03</v>
+        <v>612.53</v>
       </c>
       <c r="AC12" s="6">
-        <v>46206</v>
+        <v>46202</v>
       </c>
       <c r="AD12" s="7">
-        <v>6218.93</v>
+        <v>156.26</v>
       </c>
       <c r="AE12" s="4">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG12" s="5"/>
+        <v>197</v>
+      </c>
+      <c r="AG12" s="5" t="s">
+        <v>214</v>
+      </c>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
-      <c r="AJ12" s="4"/>
+      <c r="AJ12" s="4">
+        <v>564922714</v>
+      </c>
       <c r="AK12" s="5" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="AM12" s="6">
         <v>46153</v>
@@ -7306,194 +7306,182 @@
         <v>159</v>
       </c>
       <c r="AO12" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>523</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
       <c r="C13" s="3">
-        <v>46203</v>
+        <v>46197</v>
       </c>
       <c r="D13" s="4">
-        <v>562420916</v>
+        <v>555586629</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F13" s="6">
-        <v>46141</v>
+        <v>46118</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>208</v>
+        <v>74</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="K13" s="3">
-        <v>46251</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="K13" s="3"/>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>223</v>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v>-75</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>285</v>
+        <f ca="1">IF($F13="","",$F13+90-TODAY())</f>
+        <v>-75</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <v>94</v>
       </c>
       <c r="O13" s="6">
-        <v>46506</v>
+        <v>46208</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>78</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Z13" s="7">
-        <v>5916.4</v>
+        <v>5492.55</v>
       </c>
       <c r="AA13" s="7">
-        <v>5047.72</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="7">
-        <v>692.12</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46203</v>
+        <v>46197</v>
       </c>
       <c r="AD13" s="7">
-        <v>176.56</v>
+        <v>5492.55</v>
       </c>
       <c r="AE13" s="4">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AG13" s="5" t="s">
-        <v>185</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="AG13" s="5"/>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
-      <c r="AJ13" s="4">
-        <v>564922720</v>
-      </c>
+      <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="AM13" s="6">
-        <v>46189</v>
+        <v>46134</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO13" s="5" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>122</v>
-      </c>
+      <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3">
-        <v>46202</v>
+        <v>46127</v>
       </c>
       <c r="D14" s="4">
-        <v>557798679</v>
+        <v>565388227</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="F14" s="6">
-        <v>46142</v>
+        <v>46118</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>162</v>
+        <v>226</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>178</v>
+        <v>227</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>224</v>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>-75</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>284</v>
+        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <v>24</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>39</v>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <v>209</v>
       </c>
       <c r="O14" s="6">
-        <v>46507</v>
+        <v>46208</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="S14" s="5" t="s">
         <v>78</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>78</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
@@ -7501,121 +7489,117 @@
         <v>80</v>
       </c>
       <c r="Z14" s="7">
-        <v>6392.96</v>
+        <v>9479.4</v>
       </c>
       <c r="AA14" s="7">
-        <v>5624.17</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="7">
-        <v>612.53</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="6">
-        <v>46202</v>
+        <v>46127</v>
       </c>
       <c r="AD14" s="7">
-        <v>156.26</v>
+        <v>9479.4</v>
       </c>
       <c r="AE14" s="4">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="AG14" s="5" t="s">
-        <v>214</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="AG14" s="5"/>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
-      <c r="AJ14" s="4">
-        <v>564922714</v>
-      </c>
+      <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="AM14" s="6">
-        <v>46153</v>
+        <v>46121</v>
       </c>
       <c r="AN14" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO14" s="5" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3">
-        <v>46197</v>
+        <v>46141</v>
       </c>
       <c r="D15" s="4">
-        <v>555586629</v>
+        <v>556770603</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="F15" s="6">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-75</v>
+        <f ca="1">IF($O15="","",$O15-TODAY())</f>
+        <v>-72</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($F15="","",$F15+90-TODAY())</f>
-        <v>-75</v>
+        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
+        <v>38</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
-        <v>94</v>
+        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <v>223</v>
       </c>
       <c r="O15" s="6">
-        <v>46208</v>
+        <v>46211</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>78</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
       <c r="Y15" s="5" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="Z15" s="7">
-        <v>5492.55</v>
+        <v>2958.2</v>
       </c>
       <c r="AA15" s="7">
         <v>0</v>
@@ -7624,51 +7608,53 @@
         <v>0</v>
       </c>
       <c r="AC15" s="6">
-        <v>46197</v>
+        <v>46141</v>
       </c>
       <c r="AD15" s="7">
-        <v>5492.55</v>
+        <v>2958.2</v>
       </c>
       <c r="AE15" s="4">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="AG15" s="5"/>
+        <v>156</v>
+      </c>
+      <c r="AG15" s="5" t="s">
+        <v>233</v>
+      </c>
       <c r="AH15" s="5"/>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="AL15" s="5" t="s">
-        <v>223</v>
+        <v>83</v>
       </c>
       <c r="AM15" s="6">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="AN15" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO15" s="5" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="3">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="D16" s="4">
-        <v>565388227</v>
+        <v>556772233</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F16" s="6">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>226</v>
@@ -7677,26 +7663,26 @@
         <v>226</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-75</v>
+        <f ca="1">IF($O16="","",$O16-TODAY())</f>
+        <v>-71</v>
       </c>
       <c r="M16" s="12">
         <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" ref="N16:N28" ca="1" si="3">IF($C16="","",$C16+365-TODAY())</f>
-        <v>209</v>
+        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <v>223</v>
       </c>
       <c r="O16" s="6">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>98</v>
@@ -7717,15 +7703,15 @@
         <v>78</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>229</v>
+        <v>154</v>
       </c>
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
       <c r="Y16" s="5" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Z16" s="7">
-        <v>9479.4</v>
+        <v>5916.4</v>
       </c>
       <c r="AA16" s="7">
         <v>0</v>
@@ -7734,35 +7720,35 @@
         <v>0</v>
       </c>
       <c r="AC16" s="6">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="AD16" s="7">
-        <v>9479.4</v>
+        <v>5916.4</v>
       </c>
       <c r="AE16" s="4">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="AG16" s="5"/>
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="AL16" s="5" t="s">
         <v>83</v>
       </c>
       <c r="AM16" s="6">
-        <v>46121</v>
+        <v>46133</v>
       </c>
       <c r="AN16" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO16" s="5" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
@@ -7772,19 +7758,19 @@
         <v>46141</v>
       </c>
       <c r="D17" s="4">
-        <v>556770603</v>
+        <v>556801807</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="F17" s="6">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>74</v>
@@ -7794,28 +7780,28 @@
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-72</v>
+        <f ca="1">IF($O17="","",$O17-TODAY())</f>
+        <v>-68</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v>38</v>
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <v>223</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" ca="1" si="3"/>
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
         <v>223</v>
       </c>
       <c r="O17" s="6">
-        <v>46211</v>
+        <v>46215</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>228</v>
+        <v>99</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="S17" s="5" t="s">
         <v>78</v>
@@ -7850,84 +7836,84 @@
         <v>2958.2</v>
       </c>
       <c r="AE17" s="4">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="AF17" s="5" t="s">
         <v>156</v>
       </c>
       <c r="AG17" s="5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5" t="s">
-        <v>234</v>
+        <v>92</v>
       </c>
       <c r="AL17" s="5" t="s">
-        <v>83</v>
+        <v>241</v>
       </c>
       <c r="AM17" s="6">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="AN17" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO17" s="5" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="D18" s="4">
-        <v>556772233</v>
+        <v>556802417</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F18" s="6">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-71</v>
+        <f ca="1">IF($O18="","",$O18-TODAY())</f>
+        <v>-68</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
-        <v>38</v>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <v>252</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>223</v>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <v>252</v>
       </c>
       <c r="O18" s="6">
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="S18" s="5" t="s">
         <v>78</v>
@@ -7939,7 +7925,7 @@
         <v>78</v>
       </c>
       <c r="V18" s="5" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
@@ -7956,76 +7942,78 @@
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="AD18" s="7">
         <v>5916.4</v>
       </c>
       <c r="AE18" s="4">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AF18" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="AG18" s="5"/>
+      <c r="AG18" s="5" t="s">
+        <v>185</v>
+      </c>
       <c r="AH18" s="5"/>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
-        <v>238</v>
+        <v>92</v>
       </c>
       <c r="AL18" s="5" t="s">
-        <v>83</v>
+        <v>241</v>
       </c>
       <c r="AM18" s="6">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="AN18" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO18" s="5" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3">
-        <v>46141</v>
+        <v>46167</v>
       </c>
       <c r="D19" s="4">
-        <v>556801807</v>
+        <v>556804689</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>113</v>
+        <v>245</v>
       </c>
       <c r="F19" s="6">
         <v>46125</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O19="","",$O19-TODAY())</f>
         <v>-68</v>
       </c>
       <c r="M19" s="12">
         <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="N19" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>223</v>
+        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <v>249</v>
       </c>
       <c r="O19" s="6">
         <v>46215</v>
@@ -8034,7 +8022,7 @@
         <v>98</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="R19" s="5" t="s">
         <v>76</v>
@@ -8049,15 +8037,15 @@
         <v>78</v>
       </c>
       <c r="V19" s="5" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Z19" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AA19" s="7">
         <v>0</v>
@@ -8066,10 +8054,10 @@
         <v>0</v>
       </c>
       <c r="AC19" s="6">
-        <v>46141</v>
+        <v>46167</v>
       </c>
       <c r="AD19" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AE19" s="4">
         <v>117</v>
@@ -8078,7 +8066,7 @@
         <v>156</v>
       </c>
       <c r="AG19" s="5" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="AH19" s="5"/>
       <c r="AI19" s="5"/>
@@ -8096,7 +8084,7 @@
         <v>159</v>
       </c>
       <c r="AO19" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
@@ -8106,13 +8094,13 @@
         <v>46170</v>
       </c>
       <c r="D20" s="4">
-        <v>556802417</v>
+        <v>556801421</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F20" s="6">
-        <v>46125</v>
+        <v>46128</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>106</v>
@@ -8128,19 +8116,19 @@
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-68</v>
+        <f ca="1">IF($O20="","",$O20-TODAY())</f>
+        <v>-65</v>
       </c>
       <c r="M20" s="12">
         <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
         <v>252</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" ca="1" si="3"/>
+        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
         <v>252</v>
       </c>
       <c r="O20" s="6">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="P20" s="5" t="s">
         <v>98</v>
@@ -8184,7 +8172,7 @@
         <v>5916.4</v>
       </c>
       <c r="AE20" s="4">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AF20" s="5" t="s">
         <v>156</v>
@@ -8196,10 +8184,10 @@
       <c r="AI20" s="5"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5" t="s">
-        <v>92</v>
+        <v>248</v>
       </c>
       <c r="AL20" s="5" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="AM20" s="6">
         <v>46134</v>
@@ -8208,60 +8196,60 @@
         <v>159</v>
       </c>
       <c r="AO20" s="5" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="3">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="D21" s="4">
-        <v>556804689</v>
+        <v>561043971</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F21" s="6">
-        <v>46125</v>
+        <v>46128</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-68</v>
+        <f ca="1">IF($O21="","",$O21-TODAY())</f>
+        <v>-65</v>
       </c>
       <c r="M21" s="12">
+        <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
+        <v>53</v>
+      </c>
+      <c r="N21" s="12">
         <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>249</v>
-      </c>
-      <c r="N21" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="O21" s="6">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="S21" s="5" t="s">
         <v>78</v>
@@ -8273,15 +8261,15 @@
         <v>78</v>
       </c>
       <c r="V21" s="5" t="s">
-        <v>154</v>
+        <v>229</v>
       </c>
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Z21" s="7">
-        <v>5916.4</v>
+        <v>6392.96</v>
       </c>
       <c r="AA21" s="7">
         <v>0</v>
@@ -8290,59 +8278,57 @@
         <v>0</v>
       </c>
       <c r="AC21" s="6">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="AD21" s="7">
-        <v>5916.4</v>
+        <v>6392.96</v>
       </c>
       <c r="AE21" s="4">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AG21" s="5" t="s">
         <v>197</v>
       </c>
+      <c r="AG21" s="5"/>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5" t="s">
-        <v>92</v>
+        <v>230</v>
       </c>
       <c r="AL21" s="5" t="s">
-        <v>241</v>
+        <v>83</v>
       </c>
       <c r="AM21" s="6">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="AN21" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO21" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="3">
-        <v>46170</v>
+        <v>46143</v>
       </c>
       <c r="D22" s="4">
-        <v>556801421</v>
+        <v>565388312</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F22" s="6">
         <v>46128</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>74</v>
@@ -8352,16 +8338,16 @@
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O22="","",$O22-TODAY())</f>
         <v>-65</v>
       </c>
       <c r="M22" s="12">
+        <f ca="1">IF($C22="","",$C22+180-TODAY())</f>
+        <v>40</v>
+      </c>
+      <c r="N22" s="12">
         <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>252</v>
-      </c>
-      <c r="N22" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="O22" s="6">
         <v>46218</v>
@@ -8370,10 +8356,10 @@
         <v>98</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="S22" s="5" t="s">
         <v>78</v>
@@ -8402,7 +8388,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="6">
-        <v>46170</v>
+        <v>46143</v>
       </c>
       <c r="AD22" s="7">
         <v>5916.4</v>
@@ -8414,16 +8400,16 @@
         <v>156</v>
       </c>
       <c r="AG22" s="5" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="AL22" s="5" t="s">
-        <v>223</v>
+        <v>83</v>
       </c>
       <c r="AM22" s="6">
         <v>46134</v>
@@ -8432,23 +8418,23 @@
         <v>159</v>
       </c>
       <c r="AO22" s="5" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="3">
-        <v>46156</v>
+        <v>46141</v>
       </c>
       <c r="D23" s="4">
-        <v>561043971</v>
+        <v>556833981</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F23" s="6">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>226</v>
@@ -8460,23 +8446,23 @@
         <v>74</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>251</v>
+        <v>189</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-65</v>
+        <f ca="1">IF($O23="","",$O23-TODAY())</f>
+        <v>-61</v>
       </c>
       <c r="M23" s="12">
         <f ca="1">IF($C23="","",$C23+180-TODAY())</f>
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>238</v>
+        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <v>223</v>
       </c>
       <c r="O23" s="6">
-        <v>46218</v>
+        <v>46222</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>98</v>
@@ -8497,15 +8483,15 @@
         <v>78</v>
       </c>
       <c r="V23" s="5" t="s">
-        <v>229</v>
+        <v>174</v>
       </c>
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="Z23" s="7">
-        <v>6392.96</v>
+        <v>2958.2</v>
       </c>
       <c r="AA23" s="7">
         <v>0</v>
@@ -8514,85 +8500,91 @@
         <v>0</v>
       </c>
       <c r="AC23" s="6">
-        <v>46156</v>
+        <v>46141</v>
       </c>
       <c r="AD23" s="7">
-        <v>6392.96</v>
+        <v>2958.2</v>
       </c>
       <c r="AE23" s="4">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="AG23" s="5"/>
+        <v>156</v>
+      </c>
+      <c r="AG23" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="AL23" s="5" t="s">
         <v>83</v>
       </c>
       <c r="AM23" s="6">
-        <v>46143</v>
+        <v>46134</v>
       </c>
       <c r="AN23" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO23" s="5" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>258</v>
+      </c>
       <c r="C24" s="3">
-        <v>46143</v>
+        <v>46154</v>
       </c>
       <c r="D24" s="4">
-        <v>565388312</v>
+        <v>558609820</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="F24" s="6">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>183</v>
+        <v>261</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-65</v>
+        <f ca="1">IF($O24="","",$O24-TODAY())</f>
+        <v>-58</v>
       </c>
       <c r="M24" s="12">
         <f ca="1">IF($C24="","",$C24+180-TODAY())</f>
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>225</v>
+        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
+        <v>236</v>
       </c>
       <c r="O24" s="6">
-        <v>46218</v>
+        <v>46225</v>
       </c>
       <c r="P24" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="R24" s="5" t="s">
         <v>220</v>
@@ -8607,15 +8599,15 @@
         <v>78</v>
       </c>
       <c r="V24" s="5" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="W24" s="5"/>
       <c r="X24" s="5"/>
       <c r="Y24" s="5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Z24" s="7">
-        <v>5916.4</v>
+        <v>21135.1</v>
       </c>
       <c r="AA24" s="7">
         <v>0</v>
@@ -8623,88 +8615,84 @@
       <c r="AB24" s="7">
         <v>0</v>
       </c>
-      <c r="AC24" s="6">
-        <v>46143</v>
-      </c>
+      <c r="AC24" s="6"/>
       <c r="AD24" s="7">
-        <v>5916.4</v>
+        <v>21135.1</v>
       </c>
       <c r="AE24" s="4">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="AF24" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="AG24" s="5" t="s">
-        <v>197</v>
-      </c>
+      <c r="AG24" s="5"/>
       <c r="AH24" s="5"/>
       <c r="AI24" s="5"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="5" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="AL24" s="5" t="s">
         <v>83</v>
       </c>
       <c r="AM24" s="6">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="AN24" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO24" s="5" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3">
-        <v>46141</v>
+        <v>46156</v>
       </c>
       <c r="D25" s="4">
-        <v>556833981</v>
+        <v>557507395</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="F25" s="6">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-61</v>
+        <f ca="1">IF($O25="","",$O25-TODAY())</f>
+        <v>-54</v>
       </c>
       <c r="M25" s="12">
         <f ca="1">IF($C25="","",$C25+180-TODAY())</f>
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>223</v>
+        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
+        <v>238</v>
       </c>
       <c r="O25" s="6">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="P25" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="R25" s="5" t="s">
         <v>220</v>
@@ -8724,10 +8712,10 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
       <c r="Y25" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Z25" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AA25" s="7">
         <v>0</v>
@@ -8736,94 +8724,90 @@
         <v>0</v>
       </c>
       <c r="AC25" s="6">
-        <v>46141</v>
+        <v>46156</v>
       </c>
       <c r="AD25" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AE25" s="4">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="AF25" s="5" t="s">
         <v>156</v>
       </c>
       <c r="AG25" s="5" t="s">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="AH25" s="5"/>
       <c r="AI25" s="5"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="5" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="AL25" s="5" t="s">
-        <v>83</v>
+        <v>223</v>
       </c>
       <c r="AM25" s="6">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="AN25" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO25" s="5" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>258</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
       <c r="C26" s="3">
-        <v>46154</v>
+        <v>46217</v>
       </c>
       <c r="D26" s="4">
-        <v>558609820</v>
+        <v>562510509</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="F26" s="6">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>260</v>
+        <v>106</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>260</v>
+        <v>106</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>261</v>
+        <v>183</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-58</v>
+        <f ca="1">IF($O26="","",$O26-TODAY())</f>
+        <v>-54</v>
       </c>
       <c r="M26" s="12">
-        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
-        <v>51</v>
+        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
+        <v>299</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>236</v>
+        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
+        <v>299</v>
       </c>
       <c r="O26" s="6">
-        <v>46225</v>
+        <v>46229</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="S26" s="5" t="s">
         <v>78</v>
@@ -8835,15 +8819,15 @@
         <v>78</v>
       </c>
       <c r="V26" s="5" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
       <c r="Y26" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Z26" s="7">
-        <v>21135.1</v>
+        <v>5916.4</v>
       </c>
       <c r="AA26" s="7">
         <v>0</v>
@@ -8851,107 +8835,113 @@
       <c r="AB26" s="7">
         <v>0</v>
       </c>
-      <c r="AC26" s="6"/>
+      <c r="AC26" s="6">
+        <v>46217</v>
+      </c>
       <c r="AD26" s="7">
-        <v>21135.1</v>
+        <v>5916.4</v>
       </c>
       <c r="AE26" s="4">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AF26" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="AG26" s="5"/>
+      <c r="AG26" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="AH26" s="5"/>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="5" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="AL26" s="5" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="AM26" s="6">
-        <v>46150</v>
+        <v>46189</v>
       </c>
       <c r="AN26" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO26" s="5" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="3">
-        <v>46156</v>
+        <v>46215</v>
       </c>
       <c r="D27" s="4">
-        <v>557507395</v>
+        <v>564913658</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F27" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>183</v>
+        <v>272</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-54</v>
+        <f ca="1">IF($O27="","",$O27-TODAY())</f>
+        <v>-53</v>
       </c>
       <c r="M27" s="12">
-        <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
-        <v>53</v>
+        <f ca="1">IF($F27="","",$F27+90-TODAY())</f>
+        <v>-53</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>238</v>
+        <f ca="1">IF($C27="","",$C27+60-TODAY())</f>
+        <v>-8</v>
       </c>
       <c r="O27" s="6">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="P27" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="R27" s="5" t="s">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T27" s="5" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="U27" s="5" t="s">
         <v>78</v>
       </c>
       <c r="V27" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="W27" s="5"/>
+        <v>229</v>
+      </c>
+      <c r="W27" s="5" t="s">
+        <v>165</v>
+      </c>
       <c r="X27" s="5"/>
       <c r="Y27" s="5" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Z27" s="7">
-        <v>5916.4</v>
+        <v>4520.1099999999997</v>
       </c>
       <c r="AA27" s="7">
         <v>0</v>
@@ -8960,90 +8950,88 @@
         <v>0</v>
       </c>
       <c r="AC27" s="6">
-        <v>46156</v>
+        <v>46215</v>
       </c>
       <c r="AD27" s="7">
-        <v>5916.4</v>
+        <v>4520.1099999999997</v>
       </c>
       <c r="AE27" s="4">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF27" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AG27" s="5" t="s">
-        <v>185</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="AG27" s="5"/>
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="AL27" s="5" t="s">
-        <v>223</v>
+        <v>83</v>
       </c>
       <c r="AM27" s="6">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="AN27" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO27" s="5" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3">
-        <v>46217</v>
+        <v>46162</v>
       </c>
       <c r="D28" s="4">
-        <v>562510509</v>
+        <v>558739471</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F28" s="6">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>74</v>
+        <v>226</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-54</v>
+        <f ca="1">IF($O28="","",$O28-TODAY())</f>
+        <v>-51</v>
       </c>
       <c r="M28" s="12">
+        <f ca="1">IF($C28="","",$C28+180-TODAY())</f>
+        <v>59</v>
+      </c>
+      <c r="N28" s="12">
         <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
-        <v>299</v>
-      </c>
-      <c r="N28" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>299</v>
+        <v>244</v>
       </c>
       <c r="O28" s="6">
-        <v>46229</v>
+        <v>46232</v>
       </c>
       <c r="P28" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="S28" s="5" t="s">
         <v>78</v>
@@ -9060,10 +9048,10 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
       <c r="Y28" s="5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Z28" s="7">
-        <v>5916.4</v>
+        <v>2958.2</v>
       </c>
       <c r="AA28" s="7">
         <v>0</v>
@@ -9072,112 +9060,110 @@
         <v>0</v>
       </c>
       <c r="AC28" s="6">
-        <v>46217</v>
+        <v>46162</v>
       </c>
       <c r="AD28" s="7">
-        <v>5916.4</v>
+        <v>2958.2</v>
       </c>
       <c r="AE28" s="4">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AF28" s="5" t="s">
         <v>156</v>
       </c>
       <c r="AG28" s="5" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="AH28" s="5"/>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="AL28" s="5" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="AM28" s="6">
-        <v>46189</v>
+        <v>46153</v>
       </c>
       <c r="AN28" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO28" s="5" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="3">
-        <v>46215</v>
+        <v>46162</v>
       </c>
       <c r="D29" s="4">
-        <v>564913658</v>
+        <v>562340666</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>269</v>
+        <v>96</v>
       </c>
       <c r="F29" s="6">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>270</v>
+        <v>97</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>270</v>
+        <v>97</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>271</v>
+        <v>162</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>272</v>
+        <v>183</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-53</v>
+        <f ca="1">IF($O29="","",$O29-TODAY())</f>
+        <v>-51</v>
       </c>
       <c r="M29" s="12">
-        <f ca="1">IF($F29="","",$F29+90-TODAY())</f>
-        <v>-53</v>
+        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
+        <v>244</v>
       </c>
       <c r="N29" s="12">
-        <f ca="1">IF($C29="","",$C29+60-TODAY())</f>
-        <v>-8</v>
+        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
+        <v>244</v>
       </c>
       <c r="O29" s="6">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>273</v>
+        <v>99</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="T29" s="5" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="U29" s="5" t="s">
         <v>78</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="W29" s="5" t="s">
-        <v>165</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="W29" s="5"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="5" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="Z29" s="7">
-        <v>4520.1099999999997</v>
+        <v>5916.4</v>
       </c>
       <c r="AA29" s="7">
         <v>0</v>
@@ -9186,26 +9172,30 @@
         <v>0</v>
       </c>
       <c r="AC29" s="6">
-        <v>46215</v>
+        <v>46162</v>
       </c>
       <c r="AD29" s="7">
-        <v>4520.1099999999997</v>
+        <v>5916.4</v>
       </c>
       <c r="AE29" s="4">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AF29" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="AG29" s="5"/>
-      <c r="AH29" s="5"/>
+        <v>156</v>
+      </c>
+      <c r="AG29" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="AH29" s="5" t="s">
+        <v>279</v>
+      </c>
       <c r="AI29" s="5"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="5" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="AL29" s="5" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="AM29" s="6">
         <v>46153</v>
@@ -9214,66 +9204,66 @@
         <v>159</v>
       </c>
       <c r="AO29" s="5" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="3">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="D30" s="4">
-        <v>558739471</v>
+        <v>556762240</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F30" s="6">
-        <v>46142</v>
+        <v>46114</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-51</v>
+        <f ca="1">IF($O30="","",$O30-TODAY())</f>
+        <v>-49</v>
       </c>
       <c r="M30" s="12">
+        <f ca="1">IF($F30="","",$F30+365-TODAY())</f>
+        <v>196</v>
+      </c>
+      <c r="N30" s="12">
         <f ca="1">IF($C30="","",$C30+180-TODAY())</f>
-        <v>59</v>
-      </c>
-      <c r="N30" s="12">
-        <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
-        <v>244</v>
+        <v>51</v>
       </c>
       <c r="O30" s="6">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>228</v>
+        <v>282</v>
       </c>
       <c r="R30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="S30" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="T30" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="S30" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="T30" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="U30" s="5" t="s">
         <v>78</v>
@@ -9284,10 +9274,10 @@
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
       <c r="Y30" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Z30" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AA30" s="7">
         <v>0</v>
@@ -9296,110 +9286,92 @@
         <v>0</v>
       </c>
       <c r="AC30" s="6">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="AD30" s="7">
-        <v>2958.2</v>
+        <v>5916.4</v>
       </c>
       <c r="AE30" s="4">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="AF30" s="5" t="s">
         <v>156</v>
       </c>
       <c r="AG30" s="5" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="AH30" s="5"/>
       <c r="AI30" s="5"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="5" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="AL30" s="5" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="AM30" s="6">
-        <v>46153</v>
+        <v>46133</v>
       </c>
       <c r="AN30" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO30" s="5" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="3">
-        <v>46162</v>
-      </c>
+      <c r="B31" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" s="3"/>
       <c r="D31" s="4">
-        <v>562340666</v>
+        <v>557846752</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>96</v>
+        <v>285</v>
       </c>
       <c r="F31" s="6">
-        <v>46142</v>
+        <v>46133</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>183</v>
+        <v>286</v>
       </c>
       <c r="K31" s="3"/>
-      <c r="L31" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-51</v>
-      </c>
-      <c r="M31" s="12">
-        <f ca="1">IF($C31="","",$C31+365-TODAY())</f>
-        <v>244</v>
-      </c>
-      <c r="N31" s="12">
-        <f ca="1">IF($C31="","",$C31+365-TODAY())</f>
-        <v>244</v>
-      </c>
-      <c r="O31" s="6">
-        <v>46232</v>
-      </c>
-      <c r="P31" s="5" t="s">
-        <v>98</v>
-      </c>
+      <c r="L31" s="12" t="str">
+        <f ca="1">IF($O31="","",$O31-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="5"/>
       <c r="Q31" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="R31" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="S31" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="T31" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="U31" s="5" t="s">
-        <v>78</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
       <c r="V31" s="5" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
       <c r="Y31" s="5" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Z31" s="7">
-        <v>5916.4</v>
+        <v>5320.49</v>
       </c>
       <c r="AA31" s="7">
         <v>0</v>
@@ -9407,28 +9379,26 @@
       <c r="AB31" s="7">
         <v>0</v>
       </c>
-      <c r="AC31" s="6">
-        <v>46162</v>
-      </c>
+      <c r="AC31" s="6"/>
       <c r="AD31" s="7">
-        <v>5916.4</v>
+        <v>5320.49</v>
       </c>
       <c r="AE31" s="4">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="AF31" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="AG31" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="AH31" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="AG31" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="AH31" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="AI31" s="5"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="5" t="s">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="AL31" s="5" t="s">
         <v>102</v>
@@ -9440,80 +9410,62 @@
         <v>159</v>
       </c>
       <c r="AO31" s="5" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3">
-        <v>46154</v>
-      </c>
+      <c r="B32" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="3"/>
       <c r="D32" s="4">
-        <v>556762240</v>
+        <v>562031529</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="F32" s="6">
-        <v>46114</v>
+        <v>46133</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>282</v>
+        <v>145</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>282</v>
+        <v>145</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K32" s="3"/>
-      <c r="L32" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-49</v>
-      </c>
-      <c r="M32" s="12">
-        <f ca="1">IF($F32="","",$F32+365-TODAY())</f>
-        <v>196</v>
-      </c>
-      <c r="N32" s="12">
-        <f ca="1">IF($C32="","",$C32+180-TODAY())</f>
-        <v>51</v>
-      </c>
-      <c r="O32" s="6">
-        <v>46234</v>
-      </c>
-      <c r="P32" s="5" t="s">
-        <v>79</v>
-      </c>
+      <c r="L32" s="12" t="str">
+        <f ca="1">IF($O32="","",$O32-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="5"/>
       <c r="Q32" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="R32" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="S32" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="T32" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="U32" s="5" t="s">
-        <v>78</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
       <c r="V32" s="5" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
       <c r="Y32" s="5" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Z32" s="7">
-        <v>5916.4</v>
+        <v>6392.96</v>
       </c>
       <c r="AA32" s="7">
         <v>0</v>
@@ -9521,227 +9473,39 @@
       <c r="AB32" s="7">
         <v>0</v>
       </c>
-      <c r="AC32" s="6">
-        <v>46154</v>
-      </c>
+      <c r="AC32" s="6"/>
       <c r="AD32" s="7">
-        <v>5916.4</v>
+        <v>6392.96</v>
       </c>
       <c r="AE32" s="4">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="AF32" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AG32" s="5" t="s">
-        <v>256</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="AG32" s="5"/>
       <c r="AH32" s="5"/>
       <c r="AI32" s="5"/>
       <c r="AJ32" s="4"/>
       <c r="AK32" s="5" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AL32" s="5" t="s">
-        <v>102</v>
+        <v>293</v>
       </c>
       <c r="AM32" s="6">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="AN32" s="5" t="s">
         <v>159</v>
       </c>
       <c r="AO32" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="4">
-        <v>557846752</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F33" s="6">
-        <v>46133</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
-      <c r="U33" s="5"/>
-      <c r="V33" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="W33" s="5"/>
-      <c r="X33" s="5"/>
-      <c r="Y33" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z33" s="7">
-        <v>5320.49</v>
-      </c>
-      <c r="AA33" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="6"/>
-      <c r="AD33" s="7">
-        <v>5320.49</v>
-      </c>
-      <c r="AE33" s="4">
-        <v>109</v>
-      </c>
-      <c r="AF33" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="AG33" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="AH33" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AI33" s="5"/>
-      <c r="AJ33" s="4"/>
-      <c r="AK33" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL33" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AM33" s="6">
-        <v>46153</v>
-      </c>
-      <c r="AN33" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AO33" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="4">
-        <v>562031529</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="F34" s="6">
-        <v>46133</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
-      <c r="U34" s="5"/>
-      <c r="V34" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="W34" s="5"/>
-      <c r="X34" s="5"/>
-      <c r="Y34" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z34" s="7">
-        <v>6392.96</v>
-      </c>
-      <c r="AA34" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="6"/>
-      <c r="AD34" s="7">
-        <v>6392.96</v>
-      </c>
-      <c r="AE34" s="4">
-        <v>109</v>
-      </c>
-      <c r="AF34" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AG34" s="5"/>
-      <c r="AH34" s="5"/>
-      <c r="AI34" s="5"/>
-      <c r="AJ34" s="4"/>
-      <c r="AK34" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="AL34" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="AM34" s="6">
-        <v>46140</v>
-      </c>
-      <c r="AN34" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AO34" s="5" t="s">
         <v>294</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO34" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <conditionalFormatting sqref="L2:L34">
+  <autoFilter ref="A1:AO32" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="L2:L32">
     <cfRule type="expression" dxfId="79" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -9758,7 +9522,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M34">
+  <conditionalFormatting sqref="M2:M32">
     <cfRule type="expression" dxfId="74" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -9775,7 +9539,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N34">
+  <conditionalFormatting sqref="N2:N32">
     <cfRule type="expression" dxfId="69" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -9792,7 +9556,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U34">
+  <conditionalFormatting sqref="O2:U32">
     <cfRule type="expression" dxfId="64" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -9810,7 +9574,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A34" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A32" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9821,7 +9585,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AO8"/>
+  <dimension ref="A1:AO7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10022,7 +9786,7 @@
         <v>46278</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L8" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>29</v>
       </c>
       <c r="M2" s="12">
@@ -10146,7 +9910,7 @@
         <v>46278</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>207</v>
       </c>
       <c r="M3" s="12">
@@ -10268,7 +10032,7 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>-75</v>
       </c>
       <c r="M4" s="12">
@@ -10390,7 +10154,7 @@
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-68</v>
       </c>
       <c r="M5" s="12">
@@ -10479,22 +10243,22 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="C6" s="3">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="D6" s="4">
-        <v>567894648</v>
+        <v>558686710</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F6" s="6">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>97</v>
@@ -10503,28 +10267,28 @@
         <v>97</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K6" s="3">
         <v>46278</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-68</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>-61</v>
       </c>
       <c r="M6" s="12">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N6" s="12">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="O6" s="6">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>98</v>
@@ -10545,32 +10309,34 @@
         <v>78</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>326</v>
+        <v>299</v>
       </c>
       <c r="W6" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="X6" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Z6" s="7">
-        <v>70557.69</v>
+        <v>67599.91</v>
       </c>
       <c r="AA6" s="7">
-        <v>0</v>
+        <v>66579.55</v>
       </c>
       <c r="AB6" s="7">
-        <v>1720.81</v>
+        <v>918.36</v>
       </c>
       <c r="AC6" s="6">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="AD6" s="7">
-        <v>68836.88</v>
+        <v>102</v>
       </c>
       <c r="AE6" s="4">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="AF6" s="5" t="s">
         <v>321</v>
@@ -10582,12 +10348,14 @@
         <v>322</v>
       </c>
       <c r="AI6" s="5"/>
-      <c r="AJ6" s="4"/>
+      <c r="AJ6" s="4">
+        <v>561534376</v>
+      </c>
       <c r="AK6" s="5" t="s">
         <v>304</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AM6" s="6">
         <v>46152</v>
@@ -10596,76 +10364,58 @@
         <v>306</v>
       </c>
       <c r="AO6" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>523</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C7" s="3">
-        <v>46162</v>
+        <v>46181</v>
       </c>
       <c r="D7" s="4">
-        <v>558686710</v>
+        <v>558686759</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F7" s="6">
         <v>46132</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>97</v>
+        <v>337</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>97</v>
+        <v>337</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="K7" s="3">
-        <v>46278</v>
-      </c>
-      <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-61</v>
-      </c>
-      <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>244</v>
-      </c>
-      <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>244</v>
-      </c>
-      <c r="O7" s="6">
-        <v>46222</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>98</v>
-      </c>
+        <v>46199</v>
+      </c>
+      <c r="L7" s="4" t="str">
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="5"/>
       <c r="Q7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="T7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="U7" s="5" t="s">
-        <v>78</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
       <c r="V7" s="5" t="s">
         <v>299</v>
       </c>
@@ -10676,22 +10426,22 @@
         <v>320</v>
       </c>
       <c r="Y7" s="5" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Z7" s="7">
-        <v>67599.91</v>
+        <v>68271.210000000006</v>
       </c>
       <c r="AA7" s="7">
-        <v>66579.55</v>
+        <v>67367.5</v>
       </c>
       <c r="AB7" s="7">
-        <v>918.36</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>46162</v>
+        <v>46181</v>
       </c>
       <c r="AD7" s="7">
-        <v>102</v>
+        <v>903.71</v>
       </c>
       <c r="AE7" s="4">
         <v>110</v>
@@ -10706,9 +10456,7 @@
         <v>322</v>
       </c>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="4">
-        <v>561534376</v>
-      </c>
+      <c r="AJ7" s="4"/>
       <c r="AK7" s="5" t="s">
         <v>304</v>
       </c>
@@ -10722,118 +10470,12 @@
         <v>306</v>
       </c>
       <c r="AO7" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C8" s="3">
-        <v>46181</v>
-      </c>
-      <c r="D8" s="4">
-        <v>558686759</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46132</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="K8" s="3">
-        <v>46199</v>
-      </c>
-      <c r="L8" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="W8" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="X8" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="Y8" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="Z8" s="7">
-        <v>68271.210000000006</v>
-      </c>
-      <c r="AA8" s="7">
-        <v>67367.5</v>
-      </c>
-      <c r="AB8" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>46181</v>
-      </c>
-      <c r="AD8" s="7">
-        <v>903.71</v>
-      </c>
-      <c r="AE8" s="4">
-        <v>110</v>
-      </c>
-      <c r="AF8" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="AG8" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="AH8" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="AI8" s="5"/>
-      <c r="AJ8" s="4"/>
-      <c r="AK8" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="AL8" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="AM8" s="6">
-        <v>46152</v>
-      </c>
-      <c r="AN8" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="AO8" s="5" t="s">
         <v>340</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO8" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <conditionalFormatting sqref="L2:L8">
+  <autoFilter ref="A1:AO7" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="expression" dxfId="59" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -10850,7 +10492,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M8">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="expression" dxfId="54" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -10867,7 +10509,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N8">
+  <conditionalFormatting sqref="N2:N7">
     <cfRule type="expression" dxfId="49" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -10884,7 +10526,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U8">
+  <conditionalFormatting sqref="O2:U7">
     <cfRule type="expression" dxfId="44" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -10902,7 +10544,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A8" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A7" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10913,7 +10555,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AO21"/>
+  <dimension ref="A1:AO18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11114,7 +10756,7 @@
         <v>46279</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L21" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>200</v>
       </c>
       <c r="M2" s="12">
@@ -11230,7 +10872,7 @@
         <v>46279</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>200</v>
       </c>
       <c r="M3" s="12">
@@ -11346,7 +10988,7 @@
         <v>46279</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>210</v>
       </c>
       <c r="M4" s="12">
@@ -11460,7 +11102,7 @@
         <v>46266</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>214</v>
       </c>
       <c r="M5" s="12">
@@ -11576,7 +11218,7 @@
         <v>46278</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>217</v>
       </c>
       <c r="M6" s="12">
@@ -11694,7 +11336,7 @@
         <v>46278</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>-80</v>
       </c>
       <c r="M7" s="12">
@@ -11702,7 +11344,7 @@
         <v>115</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" ref="N7:N12" ca="1" si="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
         <v>300</v>
       </c>
       <c r="O7" s="6">
@@ -11812,7 +11454,7 @@
         <v>46269</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>-80</v>
       </c>
       <c r="M8" s="12">
@@ -11820,7 +11462,7 @@
         <v>158</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
         <v>343</v>
       </c>
       <c r="O8" s="6">
@@ -11898,58 +11540,58 @@
         <v>122</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="C9" s="3">
-        <v>46204</v>
+        <v>46141</v>
       </c>
       <c r="D9" s="4">
-        <v>566263696</v>
+        <v>556692374</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>232</v>
+        <v>374</v>
       </c>
       <c r="F9" s="6">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K9" s="3">
-        <v>46258</v>
+        <v>46278</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-75</v>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
+        <v>-68</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
-        <v>101</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>223</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>286</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>223</v>
       </c>
       <c r="O9" s="6">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>228</v>
+        <v>99</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="S9" s="5" t="s">
         <v>78</v>
@@ -11960,16 +11602,14 @@
       <c r="U9" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="V9" s="5" t="s">
-        <v>320</v>
-      </c>
+      <c r="V9" s="5"/>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5" t="s">
         <v>80</v>
       </c>
       <c r="Z9" s="7">
-        <v>6297.27</v>
+        <v>5441.29</v>
       </c>
       <c r="AA9" s="7">
         <v>0</v>
@@ -11978,23 +11618,19 @@
         <v>0</v>
       </c>
       <c r="AC9" s="6">
-        <v>46204</v>
+        <v>46141</v>
       </c>
       <c r="AD9" s="7">
-        <v>6297.27</v>
+        <v>5441.29</v>
       </c>
       <c r="AE9" s="4">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="AG9" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AH9" s="5" t="s">
-        <v>233</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
@@ -12010,66 +11646,66 @@
         <v>346</v>
       </c>
       <c r="AO9" s="5" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C10" s="3">
-        <v>46141</v>
+        <v>46252</v>
       </c>
       <c r="D10" s="4">
-        <v>556692374</v>
+        <v>556717576</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F10" s="6">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>97</v>
+        <v>384</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>97</v>
+        <v>384</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="K10" s="3">
         <v>46278</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-68</v>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
+        <v>-66</v>
       </c>
       <c r="M10" s="12">
+        <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
+        <v>149</v>
+      </c>
+      <c r="N10" s="12">
         <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>223</v>
-      </c>
-      <c r="N10" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>223</v>
+        <v>334</v>
       </c>
       <c r="O10" s="6">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>99</v>
+        <v>386</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="S10" s="5" t="s">
         <v>78</v>
@@ -12080,14 +11716,16 @@
       <c r="U10" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="V10" s="5"/>
+      <c r="V10" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="5" t="s">
         <v>80</v>
       </c>
       <c r="Z10" s="7">
-        <v>5441.29</v>
+        <v>20158.46</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -12095,36 +11733,38 @@
       <c r="AB10" s="7">
         <v>0</v>
       </c>
-      <c r="AC10" s="6">
-        <v>46141</v>
-      </c>
+      <c r="AC10" s="6"/>
       <c r="AD10" s="7">
-        <v>5441.29</v>
+        <v>20158.46</v>
       </c>
       <c r="AE10" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="AG10" s="5"/>
-      <c r="AH10" s="5"/>
+        <v>279</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="AH10" s="5" t="s">
+        <v>388</v>
+      </c>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>230</v>
+        <v>365</v>
       </c>
       <c r="AL10" s="5" t="s">
         <v>315</v>
       </c>
       <c r="AM10" s="6">
-        <v>46133</v>
+        <v>46197</v>
       </c>
       <c r="AN10" s="5" t="s">
         <v>346</v>
       </c>
       <c r="AO10" s="5" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
@@ -12132,55 +11772,55 @@
         <v>122</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="C11" s="3">
-        <v>46141</v>
+        <v>46183</v>
       </c>
       <c r="D11" s="4">
-        <v>565388366</v>
+        <v>558964326</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>225</v>
+        <v>395</v>
       </c>
       <c r="F11" s="6">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>226</v>
+        <v>384</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>226</v>
+        <v>384</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="K11" s="3">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-68</v>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
+        <v>-64</v>
       </c>
       <c r="M11" s="12">
         <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>223</v>
+        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <v>265</v>
       </c>
       <c r="O11" s="6">
-        <v>46215</v>
+        <v>46219</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>228</v>
+        <v>386</v>
       </c>
       <c r="R11" s="5" t="s">
         <v>220</v>
@@ -12201,7 +11841,7 @@
         <v>80</v>
       </c>
       <c r="Z11" s="7">
-        <v>11094.23</v>
+        <v>9056.39</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -12210,41 +11850,35 @@
         <v>0</v>
       </c>
       <c r="AC11" s="6">
-        <v>46141</v>
+        <v>46183</v>
       </c>
       <c r="AD11" s="7">
-        <v>11094.23</v>
+        <v>9056.39</v>
       </c>
       <c r="AE11" s="4">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="AG11" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="AH11" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="AI11" s="5" t="s">
-        <v>381</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="AG11" s="5"/>
+      <c r="AH11" s="5"/>
+      <c r="AI11" s="5"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>230</v>
+        <v>396</v>
       </c>
       <c r="AL11" s="5" t="s">
         <v>315</v>
       </c>
       <c r="AM11" s="6">
-        <v>46133</v>
+        <v>46153</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>346</v>
       </c>
       <c r="AO11" s="5" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
@@ -12252,64 +11886,64 @@
         <v>70</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="C12" s="3">
-        <v>46252</v>
+        <v>46202</v>
       </c>
       <c r="D12" s="4">
-        <v>556717576</v>
+        <v>563133469</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="F12" s="6">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>384</v>
+        <v>270</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>384</v>
+        <v>270</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="K12" s="3">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-66</v>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
+        <v>-58</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
-        <v>149</v>
+        <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
+        <v>-58</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>334</v>
+        <f ca="1">IF($C12="","",$C12+60-TODAY())</f>
+        <v>-21</v>
       </c>
       <c r="O12" s="6">
-        <v>46217</v>
+        <v>46225</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>386</v>
+        <v>273</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="U12" s="5" t="s">
         <v>78</v>
@@ -12331,103 +11965,103 @@
       <c r="AB12" s="7">
         <v>0</v>
       </c>
-      <c r="AC12" s="6"/>
+      <c r="AC12" s="6">
+        <v>46202</v>
+      </c>
       <c r="AD12" s="7">
         <v>20158.46</v>
       </c>
       <c r="AE12" s="4">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>279</v>
+        <v>197</v>
       </c>
       <c r="AG12" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="AH12" s="5" t="s">
-        <v>388</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>315</v>
+        <v>401</v>
       </c>
       <c r="AM12" s="6">
-        <v>46197</v>
+        <v>46147</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>346</v>
       </c>
       <c r="AO12" s="5" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>523</v>
+        <v>545</v>
       </c>
       <c r="C13" s="3">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="D13" s="4">
-        <v>556713056</v>
+        <v>558377934</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="F13" s="6">
-        <v>46128</v>
+        <v>46139</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="K13" s="3">
-        <v>46254</v>
+        <v>46278</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-65</v>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v>-54</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($F13="","",$F13+90-TODAY())</f>
-        <v>-65</v>
+        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <v>53</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
-        <v>40</v>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>238</v>
       </c>
       <c r="O13" s="6">
-        <v>46218</v>
+        <v>46229</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>78</v>
@@ -12439,7 +12073,7 @@
         <v>80</v>
       </c>
       <c r="Z13" s="7">
-        <v>2189.88</v>
+        <v>14614.67</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -12448,21 +12082,23 @@
         <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="AD13" s="7">
-        <v>2189.88</v>
+        <v>14614.67</v>
       </c>
       <c r="AE13" s="4">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>392</v>
+        <v>279</v>
       </c>
       <c r="AG13" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="AH13" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="AH13" s="5" t="s">
+        <v>406</v>
+      </c>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
@@ -12472,69 +12108,69 @@
         <v>315</v>
       </c>
       <c r="AM13" s="6">
-        <v>46133</v>
+        <v>46148</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>346</v>
       </c>
       <c r="AO13" s="5" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>544</v>
+        <v>408</v>
       </c>
       <c r="C14" s="3">
-        <v>46183</v>
+        <v>46267</v>
       </c>
       <c r="D14" s="4">
-        <v>558964326</v>
+        <v>558405759</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="F14" s="6">
-        <v>46129</v>
+        <v>46141</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>384</v>
+        <v>260</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>384</v>
+        <v>260</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>361</v>
+        <v>410</v>
       </c>
       <c r="K14" s="3">
-        <v>46278</v>
+        <v>46257</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-64</v>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>-52</v>
       </c>
       <c r="M14" s="12">
         <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="N14" s="12">
         <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
-        <v>265</v>
+        <v>349</v>
       </c>
       <c r="O14" s="6">
-        <v>46219</v>
+        <v>46231</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>386</v>
+        <v>262</v>
       </c>
       <c r="R14" s="5" t="s">
         <v>220</v>
@@ -12548,14 +12184,16 @@
       <c r="U14" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="V14" s="5"/>
+      <c r="V14" s="5" t="s">
+        <v>387</v>
+      </c>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5" t="s">
         <v>80</v>
       </c>
       <c r="Z14" s="7">
-        <v>9056.39</v>
+        <v>23841.63</v>
       </c>
       <c r="AA14" s="7">
         <v>0</v>
@@ -12563,36 +12201,40 @@
       <c r="AB14" s="7">
         <v>0</v>
       </c>
-      <c r="AC14" s="6">
-        <v>46183</v>
-      </c>
+      <c r="AC14" s="6"/>
       <c r="AD14" s="7">
-        <v>9056.39</v>
+        <v>23841.63</v>
       </c>
       <c r="AE14" s="4">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG14" s="5"/>
-      <c r="AH14" s="5"/>
-      <c r="AI14" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="AG14" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="AH14" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="AI14" s="5" t="s">
+        <v>412</v>
+      </c>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="AL14" s="5" t="s">
         <v>315</v>
       </c>
       <c r="AM14" s="6">
-        <v>46153</v>
+        <v>46184</v>
       </c>
       <c r="AN14" s="5" t="s">
         <v>346</v>
       </c>
       <c r="AO14" s="5" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
@@ -12600,64 +12242,64 @@
         <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>549</v>
+        <v>414</v>
       </c>
       <c r="C15" s="3">
-        <v>46202</v>
+        <v>46220</v>
       </c>
       <c r="D15" s="4">
-        <v>563133469</v>
+        <v>556732851</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="F15" s="6">
-        <v>46135</v>
+        <v>46113</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>270</v>
+        <v>416</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>270</v>
+        <v>416</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="K15" s="3">
-        <v>46279</v>
+        <v>46261</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-58</v>
+        <f ca="1">IF($O15="","",$O15-TODAY())</f>
+        <v>-50</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($F15="","",$F15+90-TODAY())</f>
-        <v>-58</v>
+        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
+        <v>117</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+60-TODAY())</f>
-        <v>-21</v>
+        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
+        <v>117</v>
       </c>
       <c r="O15" s="6">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>273</v>
+        <v>418</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>78</v>
@@ -12671,7 +12313,7 @@
         <v>80</v>
       </c>
       <c r="Z15" s="7">
-        <v>20158.46</v>
+        <v>23841.63</v>
       </c>
       <c r="AA15" s="7">
         <v>0</v>
@@ -12680,37 +12322,41 @@
         <v>0</v>
       </c>
       <c r="AC15" s="6">
-        <v>46202</v>
+        <v>46220</v>
       </c>
       <c r="AD15" s="7">
-        <v>20158.46</v>
+        <v>23841.63</v>
       </c>
       <c r="AE15" s="4">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>197</v>
+        <v>278</v>
       </c>
       <c r="AG15" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AH15" s="5"/>
-      <c r="AI15" s="5"/>
+        <v>419</v>
+      </c>
+      <c r="AH15" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="AI15" s="5" t="s">
+        <v>421</v>
+      </c>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5" t="s">
-        <v>400</v>
+        <v>365</v>
       </c>
       <c r="AL15" s="5" t="s">
-        <v>401</v>
+        <v>315</v>
       </c>
       <c r="AM15" s="6">
-        <v>46147</v>
+        <v>46197</v>
       </c>
       <c r="AN15" s="5" t="s">
         <v>346</v>
       </c>
       <c r="AO15" s="5" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
@@ -12718,55 +12364,55 @@
         <v>70</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C16" s="3">
-        <v>46156</v>
+        <v>46136</v>
       </c>
       <c r="D16" s="4">
-        <v>558377934</v>
+        <v>554827888</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="F16" s="6">
-        <v>46139</v>
+        <v>46115</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>260</v>
+        <v>424</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>260</v>
+        <v>424</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>404</v>
+        <v>356</v>
       </c>
       <c r="K16" s="3">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-54</v>
+        <f ca="1">IF($O16="","",$O16-TODAY())</f>
+        <v>-48</v>
       </c>
       <c r="M16" s="12">
         <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
-        <v>238</v>
+        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
+        <v>33</v>
       </c>
       <c r="O16" s="6">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>262</v>
+        <v>425</v>
       </c>
       <c r="R16" s="5" t="s">
         <v>220</v>
@@ -12775,7 +12421,7 @@
         <v>78</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="U16" s="5" t="s">
         <v>78</v>
@@ -12787,7 +12433,7 @@
         <v>80</v>
       </c>
       <c r="Z16" s="7">
-        <v>14614.67</v>
+        <v>7623.07</v>
       </c>
       <c r="AA16" s="7">
         <v>0</v>
@@ -12796,110 +12442,82 @@
         <v>0</v>
       </c>
       <c r="AC16" s="6">
-        <v>46156</v>
+        <v>46136</v>
       </c>
       <c r="AD16" s="7">
-        <v>14614.67</v>
+        <v>7623.07</v>
       </c>
       <c r="AE16" s="4">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="AG16" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="AH16" s="5" t="s">
-        <v>406</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="AG16" s="5"/>
+      <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>230</v>
+        <v>135</v>
       </c>
       <c r="AL16" s="5" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="AM16" s="6">
-        <v>46148</v>
+        <v>46119</v>
       </c>
       <c r="AN16" s="5" t="s">
         <v>346</v>
       </c>
       <c r="AO16" s="5" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C17" s="3">
-        <v>46267</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="4">
-        <v>558405759</v>
+        <v>556696226</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="F17" s="6">
-        <v>46141</v>
+        <v>46125</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>260</v>
+        <v>428</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>260</v>
+        <v>428</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="K17" s="3">
-        <v>46257</v>
-      </c>
-      <c r="L17" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-52</v>
-      </c>
-      <c r="M17" s="12">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v>164</v>
-      </c>
-      <c r="N17" s="12">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v>349</v>
-      </c>
-      <c r="O17" s="6">
-        <v>46231</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>98</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="4" t="str">
+        <f ca="1">IF($O17="","",$O17-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="5"/>
       <c r="Q17" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="R17" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="T17" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="U17" s="5" t="s">
-        <v>78</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
       <c r="V17" s="5" t="s">
-        <v>387</v>
+        <v>430</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
@@ -12907,7 +12525,7 @@
         <v>80</v>
       </c>
       <c r="Z17" s="7">
-        <v>23841.63</v>
+        <v>9768.43</v>
       </c>
       <c r="AA17" s="7">
         <v>0</v>
@@ -12917,117 +12535,91 @@
       </c>
       <c r="AC17" s="6"/>
       <c r="AD17" s="7">
-        <v>23841.63</v>
+        <v>9768.43</v>
       </c>
       <c r="AE17" s="4">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AF17" s="5" t="s">
-        <v>411</v>
+        <v>185</v>
       </c>
       <c r="AG17" s="5" t="s">
-        <v>388</v>
+        <v>197</v>
       </c>
       <c r="AH17" s="5" t="s">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="AI17" s="5" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5" t="s">
-        <v>365</v>
+        <v>230</v>
       </c>
       <c r="AL17" s="5" t="s">
         <v>315</v>
       </c>
       <c r="AM17" s="6">
-        <v>46184</v>
+        <v>46133</v>
       </c>
       <c r="AN17" s="5" t="s">
         <v>346</v>
       </c>
       <c r="AO17" s="5" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C18" s="3">
-        <v>46220</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="4">
-        <v>556732851</v>
+        <v>556723206</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="F18" s="6">
-        <v>46113</v>
+        <v>46127</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="K18" s="3">
-        <v>46261</v>
-      </c>
-      <c r="L18" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-50</v>
-      </c>
-      <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
-        <v>117</v>
-      </c>
-      <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
-        <v>117</v>
-      </c>
-      <c r="O18" s="6">
-        <v>46233</v>
-      </c>
-      <c r="P18" s="5" t="s">
-        <v>79</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="4" t="str">
+        <f ca="1">IF($O18="","",$O18-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="5"/>
       <c r="Q18" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="R18" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="T18" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="U18" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="V18" s="5" t="s">
-        <v>387</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
       <c r="Y18" s="5" t="s">
         <v>80</v>
       </c>
       <c r="Z18" s="7">
-        <v>23841.63</v>
+        <v>9056.39</v>
       </c>
       <c r="AA18" s="7">
         <v>0</v>
@@ -13035,26 +12627,24 @@
       <c r="AB18" s="7">
         <v>0</v>
       </c>
-      <c r="AC18" s="6">
-        <v>46220</v>
-      </c>
+      <c r="AC18" s="6"/>
       <c r="AD18" s="7">
-        <v>23841.63</v>
+        <v>9056.39</v>
       </c>
       <c r="AE18" s="4">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>278</v>
+        <v>357</v>
       </c>
       <c r="AG18" s="5" t="s">
-        <v>419</v>
+        <v>193</v>
       </c>
       <c r="AH18" s="5" t="s">
-        <v>420</v>
+        <v>179</v>
       </c>
       <c r="AI18" s="5" t="s">
-        <v>421</v>
+        <v>364</v>
       </c>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
@@ -13064,322 +12654,18 @@
         <v>315</v>
       </c>
       <c r="AM18" s="6">
-        <v>46197</v>
+        <v>46164</v>
       </c>
       <c r="AN18" s="5" t="s">
         <v>346</v>
       </c>
       <c r="AO18" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="C19" s="3">
-        <v>46136</v>
-      </c>
-      <c r="D19" s="4">
-        <v>554827888</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="F19" s="6">
-        <v>46115</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="K19" s="3">
-        <v>46279</v>
-      </c>
-      <c r="L19" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-48</v>
-      </c>
-      <c r="M19" s="12">
-        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
-        <v>33</v>
-      </c>
-      <c r="N19" s="12">
-        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
-        <v>33</v>
-      </c>
-      <c r="O19" s="6">
-        <v>46235</v>
-      </c>
-      <c r="P19" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="R19" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="T19" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="U19" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z19" s="7">
-        <v>7623.07</v>
-      </c>
-      <c r="AA19" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="6">
-        <v>46136</v>
-      </c>
-      <c r="AD19" s="7">
-        <v>7623.07</v>
-      </c>
-      <c r="AE19" s="4">
-        <v>127</v>
-      </c>
-      <c r="AF19" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG19" s="5"/>
-      <c r="AH19" s="5"/>
-      <c r="AI19" s="5"/>
-      <c r="AJ19" s="4"/>
-      <c r="AK19" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AL19" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="AM19" s="6">
-        <v>46119</v>
-      </c>
-      <c r="AN19" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="AO19" s="5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4">
-        <v>556696226</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="F20" s="6">
-        <v>46125</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z20" s="7">
-        <v>9768.43</v>
-      </c>
-      <c r="AA20" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="6"/>
-      <c r="AD20" s="7">
-        <v>9768.43</v>
-      </c>
-      <c r="AE20" s="4">
-        <v>117</v>
-      </c>
-      <c r="AF20" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG20" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="AH20" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="AI20" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="AJ20" s="4"/>
-      <c r="AK20" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="AL20" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="AM20" s="6">
-        <v>46133</v>
-      </c>
-      <c r="AN20" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="AO20" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4">
-        <v>556723206</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="F21" s="6">
-        <v>46127</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z21" s="7">
-        <v>9056.39</v>
-      </c>
-      <c r="AA21" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="6"/>
-      <c r="AD21" s="7">
-        <v>9056.39</v>
-      </c>
-      <c r="AE21" s="4">
-        <v>115</v>
-      </c>
-      <c r="AF21" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="AG21" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AH21" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI21" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="AJ21" s="4"/>
-      <c r="AK21" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="AL21" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="AM21" s="6">
-        <v>46164</v>
-      </c>
-      <c r="AN21" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="AO21" s="5" t="s">
         <v>435</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO21" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="L2:L21">
+  <autoFilter ref="A1:AO18" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -13396,7 +12682,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="expression" dxfId="34" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -13413,7 +12699,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="expression" dxfId="29" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -13430,7 +12716,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U21">
+  <conditionalFormatting sqref="O2:U18">
     <cfRule type="expression" dxfId="24" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -13448,7 +12734,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A21" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A18" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13459,7 +12745,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO23"/>
+  <dimension ref="A1:AO20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -13660,15 +12946,15 @@
         <v>46245</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L23" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>-37</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:N4" ca="1" si="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
         <v>96</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
         <v>96</v>
       </c>
       <c r="O2" s="6">
@@ -13776,15 +13062,15 @@
         <v>46248</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>-23</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
         <v>61</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
         <v>61</v>
       </c>
       <c r="O3" s="6">
@@ -13894,15 +13180,15 @@
         <v>46248</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>-22</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
         <v>82</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
         <v>82</v>
       </c>
       <c r="O4" s="6">
@@ -14008,7 +13294,7 @@
         <v>46248</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-21</v>
       </c>
       <c r="M5" s="12">
@@ -14089,52 +13375,52 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C6" s="3">
-        <v>46216</v>
+        <v>46157</v>
       </c>
       <c r="D6" s="4">
-        <v>558637651</v>
+        <v>558637906</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F6" s="6">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>458</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="K6" s="3">
         <v>46277</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>201</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>202</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" ref="M6:M13" ca="1" si="2">IF($C6="","",$C6+365-TODAY())</f>
-        <v>298</v>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <v>239</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ref="N6:N13" ca="1" si="3">IF($C6="","",$C6+120-TODAY())</f>
-        <v>53</v>
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <v>-6</v>
       </c>
       <c r="O6" s="6">
-        <v>46484</v>
+        <v>46485</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>76</v>
@@ -14161,41 +13447,37 @@
         <v>80</v>
       </c>
       <c r="Z6" s="7">
-        <v>879.06</v>
+        <v>3822.49</v>
       </c>
       <c r="AA6" s="7">
-        <v>785.49</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="7">
-        <v>73.08</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="6">
-        <v>46216</v>
+        <v>46157</v>
       </c>
       <c r="AD6" s="7">
-        <v>20.49</v>
+        <v>3822.49</v>
       </c>
       <c r="AE6" s="4">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AF6" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="AG6" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="AG6" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="AH6" s="5" t="s">
-        <v>460</v>
-      </c>
+      <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
-      <c r="AJ6" s="4">
-        <v>561530196</v>
-      </c>
+      <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="AM6" s="6">
         <v>46140</v>
@@ -14204,57 +13486,57 @@
         <v>441</v>
       </c>
       <c r="AO6" s="5" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C7" s="3">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="D7" s="4">
-        <v>558637906</v>
+        <v>558642115</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="F7" s="6">
-        <v>46120</v>
+        <v>46133</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>73</v>
+        <v>260</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>349</v>
+        <v>260</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="K7" s="3">
         <v>46277</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>202</v>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
+        <v>215</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>239</v>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <v>252</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
+        <v>7</v>
       </c>
       <c r="O7" s="6">
-        <v>46485</v>
+        <v>46498</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>76</v>
@@ -14284,93 +13566,97 @@
         <v>3822.49</v>
       </c>
       <c r="AA7" s="7">
-        <v>0</v>
+        <v>3388.74</v>
       </c>
       <c r="AB7" s="7">
-        <v>0</v>
+        <v>338.78</v>
       </c>
       <c r="AC7" s="6">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="AD7" s="7">
-        <v>3822.49</v>
+        <v>94.97</v>
       </c>
       <c r="AE7" s="4">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AG7" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="AH7" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="4"/>
+      <c r="AJ7" s="4">
+        <v>561714739</v>
+      </c>
       <c r="AK7" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>241</v>
+        <v>102</v>
       </c>
       <c r="AM7" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AO7" s="5" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C8" s="3">
-        <v>46184</v>
+        <v>46155</v>
       </c>
       <c r="D8" s="4">
-        <v>558640479</v>
+        <v>557577339</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F8" s="6">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="K8" s="3">
         <v>46277</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>209</v>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
+        <v>216</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>266</v>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v>237</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
+        <v>-8</v>
       </c>
       <c r="O8" s="6">
-        <v>46492</v>
+        <v>46499</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>76</v>
@@ -14397,33 +13683,35 @@
         <v>80</v>
       </c>
       <c r="Z8" s="7">
-        <v>879.06</v>
+        <v>1294.23</v>
       </c>
       <c r="AA8" s="7">
-        <v>809.52</v>
+        <v>1127.69</v>
       </c>
       <c r="AB8" s="7">
-        <v>100.89</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="AC8" s="6">
-        <v>46184</v>
+        <v>46155</v>
       </c>
       <c r="AD8" s="7">
-        <v>-25.92</v>
+        <v>35.74</v>
       </c>
       <c r="AE8" s="4">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>450</v>
+        <v>197</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="AH8" s="5"/>
+        <v>473</v>
+      </c>
+      <c r="AH8" s="5" t="s">
+        <v>474</v>
+      </c>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4">
-        <v>561532204</v>
+        <v>560552425</v>
       </c>
       <c r="AK8" s="5" t="s">
         <v>131</v>
@@ -14438,57 +13726,57 @@
         <v>441</v>
       </c>
       <c r="AO8" s="5" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C9" s="3">
-        <v>46170</v>
+        <v>46154</v>
       </c>
       <c r="D9" s="4">
-        <v>558642115</v>
+        <v>558245138</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="F9" s="6">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>260</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>260</v>
+        <v>477</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="K9" s="3">
         <v>46277</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>215</v>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
+        <v>222</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>252</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>236</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <v>-9</v>
       </c>
       <c r="O9" s="6">
-        <v>46498</v>
+        <v>46505</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>76</v>
@@ -14515,36 +13803,30 @@
         <v>80</v>
       </c>
       <c r="Z9" s="7">
-        <v>3822.49</v>
+        <v>3486.42</v>
       </c>
       <c r="AA9" s="7">
-        <v>3388.74</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="7">
-        <v>338.78</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="6">
-        <v>46170</v>
+        <v>46154</v>
       </c>
       <c r="AD9" s="7">
-        <v>94.97</v>
+        <v>3486.42</v>
       </c>
       <c r="AE9" s="4">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="AG9" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="AH9" s="5" t="s">
-        <v>450</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
-      <c r="AJ9" s="4">
-        <v>561714739</v>
-      </c>
+      <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
         <v>135</v>
       </c>
@@ -14552,36 +13834,36 @@
         <v>102</v>
       </c>
       <c r="AM9" s="6">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="AN9" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AO9" s="5" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C10" s="3">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="D10" s="4">
-        <v>557577339</v>
+        <v>558246366</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="F10" s="6">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>73</v>
@@ -14596,19 +13878,19 @@
         <v>46277</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>216</v>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
+        <v>223</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>237</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>236</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
+        <v>-9</v>
       </c>
       <c r="O10" s="6">
-        <v>46499</v>
+        <v>46506</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>76</v>
@@ -14638,33 +13920,27 @@
         <v>1294.23</v>
       </c>
       <c r="AA10" s="7">
-        <v>1127.69</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="7">
-        <v>130.80000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="6">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="AD10" s="7">
-        <v>35.74</v>
+        <v>1294.23</v>
       </c>
       <c r="AE10" s="4">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>474</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
-      <c r="AJ10" s="4">
-        <v>560552425</v>
-      </c>
+      <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
         <v>131</v>
       </c>
@@ -14672,13 +13948,13 @@
         <v>241</v>
       </c>
       <c r="AM10" s="6">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="AN10" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AO10" s="5" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
@@ -14692,13 +13968,13 @@
         <v>46154</v>
       </c>
       <c r="D11" s="4">
-        <v>558245138</v>
+        <v>558247000</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="F11" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>73</v>
@@ -14707,28 +13983,28 @@
         <v>73</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>477</v>
+        <v>97</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="K11" s="3">
         <v>46277</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>222</v>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
+        <v>223</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
         <v>236</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" ca="1" si="3"/>
+        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
         <v>-9</v>
       </c>
       <c r="O11" s="6">
-        <v>46505</v>
+        <v>46506</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>76</v>
@@ -14755,7 +14031,7 @@
         <v>80</v>
       </c>
       <c r="Z11" s="7">
-        <v>3486.42</v>
+        <v>2173.29</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -14767,23 +14043,23 @@
         <v>46154</v>
       </c>
       <c r="AD11" s="7">
-        <v>3486.42</v>
+        <v>2173.29</v>
       </c>
       <c r="AE11" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="AM11" s="6">
         <v>46147</v>
@@ -14792,7 +14068,7 @@
         <v>441</v>
       </c>
       <c r="AO11" s="5" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
@@ -14800,64 +14076,64 @@
         <v>70</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>524</v>
+        <v>553</v>
       </c>
       <c r="C12" s="3">
-        <v>46154</v>
+        <v>46216</v>
       </c>
       <c r="D12" s="4">
-        <v>558246366</v>
+        <v>558304247</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F12" s="6">
-        <v>46141</v>
+        <v>46114</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="K12" s="3">
-        <v>46277</v>
+        <v>46282</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>223</v>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
+        <v>-79</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>236</v>
+        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <v>113</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <v>298</v>
       </c>
       <c r="O12" s="6">
-        <v>46506</v>
+        <v>46204</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="S12" s="5" t="s">
         <v>78</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="U12" s="5" t="s">
         <v>78</v>
@@ -14869,7 +14145,7 @@
         <v>80</v>
       </c>
       <c r="Z12" s="7">
-        <v>1294.23</v>
+        <v>2173.29</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -14878,35 +14154,39 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46154</v>
+        <v>46218</v>
       </c>
       <c r="AD12" s="7">
-        <v>1294.23</v>
+        <v>2173.29</v>
       </c>
       <c r="AE12" s="4">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="AG12" s="5"/>
-      <c r="AH12" s="5"/>
+        <v>488</v>
+      </c>
+      <c r="AG12" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="AH12" s="5" t="s">
+        <v>489</v>
+      </c>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>241</v>
+        <v>455</v>
       </c>
       <c r="AM12" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AO12" s="5" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
@@ -14914,55 +14194,55 @@
         <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="C13" s="3">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="D13" s="4">
-        <v>558247000</v>
+        <v>558637485</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="F13" s="6">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="K13" s="3">
-        <v>46277</v>
+        <v>46283</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>223</v>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v>-74</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>236</v>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>246</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>246</v>
       </c>
       <c r="O13" s="6">
-        <v>46506</v>
+        <v>46209</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="R13" s="5" t="s">
         <v>76</v>
@@ -14971,7 +14251,7 @@
         <v>78</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>78</v>
@@ -14991,36 +14271,36 @@
       <c r="AB13" s="7">
         <v>0</v>
       </c>
-      <c r="AC13" s="6">
-        <v>46154</v>
-      </c>
+      <c r="AC13" s="6"/>
       <c r="AD13" s="7">
         <v>2173.29</v>
       </c>
       <c r="AE13" s="4">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="AG13" s="5"/>
+        <v>492</v>
+      </c>
+      <c r="AG13" s="5" t="s">
+        <v>440</v>
+      </c>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>241</v>
+        <v>102</v>
       </c>
       <c r="AM13" s="6">
-        <v>46147</v>
+        <v>46140</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AO13" s="5" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
@@ -15028,55 +14308,55 @@
         <v>70</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>553</v>
+        <v>526</v>
       </c>
       <c r="C14" s="3">
-        <v>46216</v>
+        <v>46184</v>
       </c>
       <c r="D14" s="4">
-        <v>558304247</v>
+        <v>558308311</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F14" s="6">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="K14" s="3">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-79</v>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>-72</v>
       </c>
       <c r="M14" s="12">
         <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" ref="N14:N21" ca="1" si="4">IF($C14="","",$C14+365-TODAY())</f>
-        <v>298</v>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <v>266</v>
       </c>
       <c r="O14" s="6">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="R14" s="5" t="s">
         <v>220</v>
@@ -15097,7 +14377,7 @@
         <v>80</v>
       </c>
       <c r="Z14" s="7">
-        <v>2173.29</v>
+        <v>1294.23</v>
       </c>
       <c r="AA14" s="7">
         <v>0</v>
@@ -15106,23 +14386,21 @@
         <v>0</v>
       </c>
       <c r="AC14" s="6">
-        <v>46218</v>
+        <v>46184</v>
       </c>
       <c r="AD14" s="7">
-        <v>2173.29</v>
+        <v>1294.23</v>
       </c>
       <c r="AE14" s="4">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="AG14" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="AH14" s="5" t="s">
-        <v>489</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
@@ -15138,7 +14416,7 @@
         <v>441</v>
       </c>
       <c r="AO14" s="5" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
@@ -15146,58 +14424,58 @@
         <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>554</v>
+        <v>527</v>
       </c>
       <c r="C15" s="3">
-        <v>46164</v>
+        <v>46224</v>
       </c>
       <c r="D15" s="4">
-        <v>558637485</v>
+        <v>558638750</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="F15" s="6">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>74</v>
+        <v>498</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="K15" s="3">
-        <v>46283</v>
+        <v>46278</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-74</v>
+        <f ca="1">IF($O15="","",$O15-TODAY())</f>
+        <v>-72</v>
       </c>
       <c r="M15" s="12">
+        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
+        <v>121</v>
+      </c>
+      <c r="N15" s="12">
         <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
-        <v>246</v>
-      </c>
-      <c r="N15" s="12">
-        <f t="shared" ca="1" si="4"/>
-        <v>246</v>
+        <v>306</v>
       </c>
       <c r="O15" s="6">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>78</v>
@@ -15215,7 +14493,7 @@
         <v>80</v>
       </c>
       <c r="Z15" s="7">
-        <v>2173.29</v>
+        <v>3822.49</v>
       </c>
       <c r="AA15" s="7">
         <v>0</v>
@@ -15223,36 +14501,36 @@
       <c r="AB15" s="7">
         <v>0</v>
       </c>
-      <c r="AC15" s="6"/>
+      <c r="AC15" s="6">
+        <v>46224</v>
+      </c>
       <c r="AD15" s="7">
-        <v>2173.29</v>
+        <v>3822.49</v>
       </c>
       <c r="AE15" s="4">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="AG15" s="5" t="s">
-        <v>440</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="AG15" s="5"/>
       <c r="AH15" s="5"/>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="4"/>
       <c r="AK15" s="5" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="AL15" s="5" t="s">
-        <v>102</v>
+        <v>455</v>
       </c>
       <c r="AM15" s="6">
-        <v>46140</v>
+        <v>46150</v>
       </c>
       <c r="AN15" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AO15" s="5" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
@@ -15260,19 +14538,19 @@
         <v>70</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C16" s="3">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="D16" s="4">
-        <v>558308311</v>
+        <v>565376983</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="F16" s="6">
-        <v>46121</v>
+        <v>46135</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>260</v>
@@ -15284,25 +14562,23 @@
         <v>74</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="K16" s="3">
-        <v>46278</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="K16" s="3"/>
       <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-72</v>
+        <f ca="1">IF($O16="","",$O16-TODAY())</f>
+        <v>-58</v>
       </c>
       <c r="M16" s="12">
         <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" ca="1" si="4"/>
-        <v>266</v>
+        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <v>259</v>
       </c>
       <c r="O16" s="6">
-        <v>46211</v>
+        <v>46225</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>98</v>
@@ -15329,7 +14605,7 @@
         <v>80</v>
       </c>
       <c r="Z16" s="7">
-        <v>1294.23</v>
+        <v>2943.43</v>
       </c>
       <c r="AA16" s="7">
         <v>0</v>
@@ -15338,20 +14614,18 @@
         <v>0</v>
       </c>
       <c r="AC16" s="6">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="AD16" s="7">
-        <v>1294.23</v>
+        <v>2943.43</v>
       </c>
       <c r="AE16" s="4">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="AG16" s="5" t="s">
-        <v>495</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="AG16" s="5"/>
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4"/>
@@ -15368,66 +14642,64 @@
         <v>441</v>
       </c>
       <c r="AO16" s="5" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C17" s="3">
-        <v>46224</v>
+        <v>46152</v>
       </c>
       <c r="D17" s="4">
-        <v>558638750</v>
+        <v>558643419</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="F17" s="6">
-        <v>46121</v>
+        <v>46142</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>498</v>
+        <v>213</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="K17" s="3">
-        <v>46278</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="K17" s="3"/>
       <c r="L17" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-72</v>
+        <f ca="1">IF($O17="","",$O17-TODAY())</f>
+        <v>-51</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
-        <v>121</v>
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <v>234</v>
       </c>
       <c r="N17" s="12">
-        <f t="shared" ca="1" si="4"/>
-        <v>306</v>
+        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <v>234</v>
       </c>
       <c r="O17" s="6">
-        <v>46211</v>
+        <v>46232</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>98</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="S17" s="5" t="s">
         <v>78</v>
@@ -15445,30 +14717,32 @@
         <v>80</v>
       </c>
       <c r="Z17" s="7">
-        <v>3822.49</v>
+        <v>1649.2</v>
       </c>
       <c r="AA17" s="7">
-        <v>0</v>
+        <v>1454.49</v>
       </c>
       <c r="AB17" s="7">
-        <v>0</v>
+        <v>59.71</v>
       </c>
       <c r="AC17" s="6">
-        <v>46224</v>
+        <v>46152</v>
       </c>
       <c r="AD17" s="7">
-        <v>3822.49</v>
+        <v>135</v>
       </c>
       <c r="AE17" s="4">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="AF17" s="5" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="AG17" s="5"/>
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
-      <c r="AJ17" s="4"/>
+      <c r="AJ17" s="4">
+        <v>561157100</v>
+      </c>
       <c r="AK17" s="5" t="s">
         <v>120</v>
       </c>
@@ -15476,33 +14750,33 @@
         <v>455</v>
       </c>
       <c r="AM17" s="6">
-        <v>46150</v>
+        <v>46148</v>
       </c>
       <c r="AN17" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AO17" s="5" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="C18" s="3">
-        <v>46188</v>
+        <v>46160</v>
       </c>
       <c r="D18" s="4">
-        <v>561540981</v>
+        <v>558643981</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="F18" s="6">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>226</v>
@@ -15514,25 +14788,25 @@
         <v>74</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>501</v>
+        <v>439</v>
       </c>
       <c r="K18" s="3">
-        <v>46253</v>
+        <v>46278</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-58</v>
+        <f ca="1">IF($O18="","",$O18-TODAY())</f>
+        <v>-51</v>
       </c>
       <c r="M18" s="12">
         <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" ca="1" si="4"/>
-        <v>270</v>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <v>242</v>
       </c>
       <c r="O18" s="6">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>98</v>
@@ -15559,30 +14833,32 @@
         <v>80</v>
       </c>
       <c r="Z18" s="7">
-        <v>2943.43</v>
+        <v>879.06</v>
       </c>
       <c r="AA18" s="7">
-        <v>-389.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="7">
-        <v>389.2</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <v>46188</v>
+        <v>46160</v>
       </c>
       <c r="AD18" s="7">
-        <v>2943.43</v>
+        <v>879.06</v>
       </c>
       <c r="AE18" s="4">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="AG18" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="AH18" s="5"/>
+        <v>460</v>
+      </c>
+      <c r="AH18" s="5" t="s">
+        <v>459</v>
+      </c>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
@@ -15598,7 +14874,7 @@
         <v>441</v>
       </c>
       <c r="AO18" s="5" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
@@ -15606,62 +14882,55 @@
         <v>70</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C19" s="3">
-        <v>46177</v>
+        <v>46153</v>
       </c>
       <c r="D19" s="4">
-        <v>565376983</v>
+        <v>558622490</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="F19" s="6">
-        <v>46135</v>
+        <v>46113</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>260</v>
+        <v>512</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>260</v>
+        <v>512</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>74</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-58</v>
-      </c>
-      <c r="M19" s="12">
-        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
-        <v>74</v>
-      </c>
+        <f ca="1">IF($O19="","",$O19-TODAY())</f>
+        <v>-50</v>
+      </c>
+      <c r="M19" s="12"/>
       <c r="N19" s="12">
-        <f t="shared" ca="1" si="4"/>
-        <v>259</v>
+        <f ca="1">IF($C19="","",$C19+65-TODAY())</f>
+        <v>-65</v>
       </c>
       <c r="O19" s="6">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="R19" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>78</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
       <c r="T19" s="5" t="s">
-        <v>76</v>
+        <v>515</v>
       </c>
       <c r="U19" s="5" t="s">
         <v>78</v>
@@ -15673,7 +14942,7 @@
         <v>80</v>
       </c>
       <c r="Z19" s="7">
-        <v>2943.43</v>
+        <v>3822.49</v>
       </c>
       <c r="AA19" s="7">
         <v>0</v>
@@ -15682,98 +14951,93 @@
         <v>0</v>
       </c>
       <c r="AC19" s="6">
-        <v>46177</v>
+        <v>46153</v>
       </c>
       <c r="AD19" s="7">
-        <v>2943.43</v>
+        <v>3822.49</v>
       </c>
       <c r="AE19" s="4">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="AG19" s="5"/>
-      <c r="AH19" s="5"/>
-      <c r="AI19" s="5"/>
+        <v>516</v>
+      </c>
+      <c r="AG19" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="AH19" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI19" s="5" t="s">
+        <v>179</v>
+      </c>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="AL19" s="5" t="s">
-        <v>455</v>
+        <v>241</v>
       </c>
       <c r="AM19" s="6">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="AN19" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AO19" s="5" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
       <c r="C20" s="3">
-        <v>46152</v>
+        <v>46157</v>
       </c>
       <c r="D20" s="4">
-        <v>558643419</v>
+        <v>557575573</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="F20" s="6">
-        <v>46142</v>
+        <v>46134</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>213</v>
+        <v>519</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>106</v>
+        <v>519</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>507</v>
       </c>
       <c r="K20" s="3"/>
-      <c r="L20" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-51</v>
-      </c>
-      <c r="M20" s="12">
-        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
-        <v>234</v>
-      </c>
+      <c r="L20" s="12" t="str">
+        <f ca="1">IF($O20="","",$O20-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M20" s="12"/>
       <c r="N20" s="12">
-        <f t="shared" ca="1" si="4"/>
-        <v>234</v>
-      </c>
-      <c r="O20" s="6">
-        <v>46232</v>
-      </c>
-      <c r="P20" s="5" t="s">
-        <v>98</v>
-      </c>
+        <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
+        <v>54</v>
+      </c>
+      <c r="O20" s="6"/>
+      <c r="P20" s="5"/>
       <c r="Q20" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="R20" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="S20" s="5" t="s">
-        <v>78</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
       <c r="T20" s="5" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="U20" s="5" t="s">
         <v>78</v>
@@ -15788,382 +15052,50 @@
         <v>1649.2</v>
       </c>
       <c r="AA20" s="7">
-        <v>1454.49</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="7">
-        <v>59.71</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="6">
-        <v>46152</v>
+        <v>46157</v>
       </c>
       <c r="AD20" s="7">
-        <v>135</v>
+        <v>1649.2</v>
       </c>
       <c r="AE20" s="4">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="AF20" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="AG20" s="5"/>
-      <c r="AH20" s="5"/>
+        <v>460</v>
+      </c>
+      <c r="AG20" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="AH20" s="5" t="s">
+        <v>454</v>
+      </c>
       <c r="AI20" s="5"/>
-      <c r="AJ20" s="4">
-        <v>561157100</v>
-      </c>
+      <c r="AJ20" s="4"/>
       <c r="AK20" s="5" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="AL20" s="5" t="s">
-        <v>455</v>
+        <v>241</v>
       </c>
       <c r="AM20" s="6">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="AN20" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AO20" s="5" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="C21" s="3">
-        <v>46160</v>
-      </c>
-      <c r="D21" s="4">
-        <v>558643981</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="F21" s="6">
-        <v>46142</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="K21" s="3">
-        <v>46278</v>
-      </c>
-      <c r="L21" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-51</v>
-      </c>
-      <c r="M21" s="12">
-        <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
-        <v>57</v>
-      </c>
-      <c r="N21" s="12">
-        <f t="shared" ca="1" si="4"/>
-        <v>242</v>
-      </c>
-      <c r="O21" s="6">
-        <v>46232</v>
-      </c>
-      <c r="P21" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q21" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="R21" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="S21" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="T21" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="U21" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z21" s="7">
-        <v>879.06</v>
-      </c>
-      <c r="AA21" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="6">
-        <v>46160</v>
-      </c>
-      <c r="AD21" s="7">
-        <v>879.06</v>
-      </c>
-      <c r="AE21" s="4">
-        <v>100</v>
-      </c>
-      <c r="AF21" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="AG21" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="AH21" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="AI21" s="5"/>
-      <c r="AJ21" s="4"/>
-      <c r="AK21" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL21" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="AM21" s="6">
-        <v>46148</v>
-      </c>
-      <c r="AN21" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="AO21" s="5" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C22" s="3">
-        <v>46153</v>
-      </c>
-      <c r="D22" s="4">
-        <v>558622490</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="F22" s="6">
-        <v>46113</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-50</v>
-      </c>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12">
-        <f ca="1">IF($C22="","",$C22+65-TODAY())</f>
-        <v>-65</v>
-      </c>
-      <c r="O22" s="6">
-        <v>46233</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="U22" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z22" s="7">
-        <v>3822.49</v>
-      </c>
-      <c r="AA22" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="6">
-        <v>46153</v>
-      </c>
-      <c r="AD22" s="7">
-        <v>3822.49</v>
-      </c>
-      <c r="AE22" s="4">
-        <v>129</v>
-      </c>
-      <c r="AF22" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="AG22" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="AH22" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AI22" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="AJ22" s="4"/>
-      <c r="AK22" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="AL22" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AM22" s="6">
-        <v>46140</v>
-      </c>
-      <c r="AN22" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="AO22" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="C23" s="3">
-        <v>46157</v>
-      </c>
-      <c r="D23" s="4">
-        <v>557575573</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="F23" s="6">
-        <v>46134</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12">
-        <f ca="1">IF($C23="","",$C23+180-TODAY())</f>
-        <v>54</v>
-      </c>
-      <c r="O23" s="6"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="U23" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z23" s="7">
-        <v>1649.2</v>
-      </c>
-      <c r="AA23" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="6">
-        <v>46157</v>
-      </c>
-      <c r="AD23" s="7">
-        <v>1649.2</v>
-      </c>
-      <c r="AE23" s="4">
-        <v>108</v>
-      </c>
-      <c r="AF23" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="AG23" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="AH23" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="AI23" s="5"/>
-      <c r="AJ23" s="4"/>
-      <c r="AK23" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="AL23" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AM23" s="6">
-        <v>46141</v>
-      </c>
-      <c r="AN23" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="AO23" s="5" t="s">
         <v>521</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO23" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
-  <conditionalFormatting sqref="L2:L23">
+  <autoFilter ref="A1:AO20" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -16180,7 +15112,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="14" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -16197,7 +15129,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -16214,7 +15146,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U23">
+  <conditionalFormatting sqref="O2:U20">
     <cfRule type="expression" dxfId="4" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -16232,7 +15164,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A23" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A20" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="578">
   <si>
     <t>2026-04 April - Specialty Claims</t>
   </si>
@@ -2773,6 +2773,45 @@
   </si>
   <si>
     <t>***Shift to PT if I find same and similar on portal  - ABN signed - Another L0650 was dispensed back on 04/25/2022 - Supplier SONOSPINE ARIZONA LLC - DND L0650 M3 Equipment is the same or similar to equipment already being used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for account to get activated again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shift to PT if I find same and similar on portal  - ABN signed - Another L0650 was dispensed back on 04/25/2022 - Supplier SONOSPINE ARIZONA LLC - DND L0650 M3 Equipment is the same or similar to equipment already being used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chat with ins to confirm covarage - ABN signed - charges per ins contract - PR non covered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DND 75710 This procedure or procedure/modifier combination is not compatible with another procedure or procedure/modifier combination provided on the same day according to the National Correct Coding Initiative or workers compensation state regulations/ fee schedule requirements - Adjusted balance for 36246 not included in the auth requested - 36248 add on requires payment for other cpt code - 99153 cant be billed on pos 24 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DND 36248 due to exceeded MUE - DND 36245, 36246, and 75710 due to invalid dx </t>
+  </si>
+  <si>
+    <t xml:space="preserve">trying to get access to EOB with imperial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">no access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">START A CHAT AND ASK FOR A PIQ REVIEW OR STATUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secondary - check cob on noridian, if nothing there, check with April - 1A95CU0TY97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send pending msm to Bri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for Bri's reply - Juan sent MR to me </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
 </sst>
 </file>
@@ -4330,7 +4369,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>16</v>
+        <v>577</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">
@@ -5603,9 +5642,11 @@
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>565</v>
+      </c>
       <c r="B11" s="2" t="s">
-        <v>143</v>
+        <v>566</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4">
@@ -5691,9 +5732,11 @@
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>565</v>
+      </c>
       <c r="B12" s="2" t="s">
-        <v>143</v>
+        <v>566</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4">
@@ -5851,7 +5894,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A12" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6733,10 +6776,10 @@
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>565</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C8" s="3">
         <v>46148</v>
@@ -8535,10 +8578,10 @@
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>565</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>258</v>
+        <v>568</v>
       </c>
       <c r="C24" s="3">
         <v>46154</v>
@@ -9320,9 +9363,11 @@
       </c>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>565</v>
+      </c>
       <c r="B31" s="2" t="s">
-        <v>143</v>
+        <v>566</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="4">
@@ -9414,9 +9459,11 @@
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>565</v>
+      </c>
       <c r="B32" s="2" t="s">
-        <v>143</v>
+        <v>566</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="4">
@@ -9575,7 +9622,7 @@
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A32" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10001,10 +10048,10 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>565</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>533</v>
+        <v>569</v>
       </c>
       <c r="C4" s="3">
         <v>46165</v>
@@ -10123,10 +10170,10 @@
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>565</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
       <c r="C5" s="3">
         <v>46162</v>
@@ -10545,7 +10592,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A7" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12474,9 +12521,11 @@
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>565</v>
+      </c>
       <c r="B17" s="2" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="4">
@@ -12570,9 +12619,11 @@
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>565</v>
+      </c>
       <c r="B18" s="2" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="4">
@@ -12735,7 +12786,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A18" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14535,10 +14586,10 @@
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>565</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>528</v>
+        <v>573</v>
       </c>
       <c r="C16" s="3">
         <v>46177</v>
@@ -14647,10 +14698,10 @@
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>86</v>
+        <v>565</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>529</v>
+        <v>574</v>
       </c>
       <c r="C17" s="3">
         <v>46152</v>
@@ -14879,10 +14930,10 @@
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>565</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="C19" s="3">
         <v>46153</v>
@@ -14990,10 +15041,10 @@
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>565</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="C20" s="3">
         <v>46157</v>
@@ -15165,7 +15216,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A20" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2122" uniqueCount="579">
   <si>
     <t>2026-04 April - Specialty Claims</t>
   </si>
@@ -2812,6 +2812,9 @@
   </si>
   <si>
     <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540 days</t>
   </si>
 </sst>
 </file>
@@ -4652,11 +4655,11 @@
         <v>46265</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L12" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>195</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M7" ca="1" si="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
         <v>239</v>
       </c>
       <c r="N2" s="12">
@@ -4762,11 +4765,11 @@
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>215</v>
       </c>
       <c r="M3" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
         <v/>
       </c>
       <c r="N3" s="12" t="str">
@@ -4878,12 +4881,12 @@
         <v>46231</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>-80</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>244</v>
+        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <v>-80</v>
       </c>
       <c r="N4" s="12">
         <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
@@ -4899,10 +4902,10 @@
         <v>99</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T4" s="5" t="s">
         <v>76</v>
@@ -4992,11 +4995,11 @@
         <v>46257</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-66</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
         <v>344</v>
       </c>
       <c r="N5" s="12">
@@ -5104,12 +5107,12 @@
         <v>46276</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>-61</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>239</v>
+        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
+        <v>-61</v>
       </c>
       <c r="N6" s="12">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
@@ -5125,10 +5128,10 @@
         <v>99</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T6" s="5" t="s">
         <v>76</v>
@@ -5218,11 +5221,11 @@
         <v>46265</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>-59</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
         <v>249</v>
       </c>
       <c r="N7" s="12">
@@ -5334,7 +5337,7 @@
         <v>46265</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>-58</v>
       </c>
       <c r="M8" s="12">
@@ -5342,8 +5345,8 @@
         <v>-58</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+60-TODAY())</f>
-        <v>-66</v>
+        <f ca="1">IF($C8="","",$C8+540-TODAY())</f>
+        <v>414</v>
       </c>
       <c r="O8" s="6">
         <v>46225</v>
@@ -5361,7 +5364,7 @@
         <v>129</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>130</v>
+        <v>578</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>78</v>
@@ -5450,7 +5453,7 @@
         <v>46265</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
         <v>-57</v>
       </c>
       <c r="M9" s="12">
@@ -5564,7 +5567,7 @@
         <v>46257</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
         <v>-43</v>
       </c>
       <c r="M10" s="12">
@@ -5672,7 +5675,7 @@
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
         <v/>
       </c>
       <c r="M11" s="12"/>
@@ -5762,7 +5765,7 @@
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
         <v/>
       </c>
       <c r="M12" s="12"/>
@@ -7827,8 +7830,8 @@
         <v>-68</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v>223</v>
+        <f ca="1">IF($F17="","",$F17+90-TODAY())</f>
+        <v>-68</v>
       </c>
       <c r="N17" s="12">
         <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
@@ -7844,10 +7847,10 @@
         <v>99</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>76</v>
@@ -9169,8 +9172,8 @@
         <v>-51</v>
       </c>
       <c r="M29" s="12">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>244</v>
+        <f ca="1">IF($F29="","",$F29+90-TODAY())</f>
+        <v>-51</v>
       </c>
       <c r="N29" s="12">
         <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
@@ -9186,10 +9189,10 @@
         <v>99</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T29" s="5" t="s">
         <v>76</v>
@@ -10087,8 +10090,8 @@
         <v>-75</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+60-TODAY())</f>
-        <v>-58</v>
+        <f ca="1">IF($C4="","",$C4+540-TODAY())</f>
+        <v>422</v>
       </c>
       <c r="O4" s="6">
         <v>46208</v>
@@ -10106,7 +10109,7 @@
         <v>129</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>130</v>
+        <v>578</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>78</v>
@@ -10327,8 +10330,8 @@
         <v>-61</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>244</v>
+        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
+        <v>-61</v>
       </c>
       <c r="N6" s="12">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
@@ -10344,10 +10347,10 @@
         <v>99</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T6" s="5" t="s">
         <v>76</v>
@@ -11621,8 +11624,8 @@
         <v>-68</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>223</v>
+        <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
+        <v>-68</v>
       </c>
       <c r="N9" s="12">
         <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
@@ -11638,10 +11641,10 @@
         <v>99</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>76</v>
@@ -14279,8 +14282,8 @@
         <v>-74</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v>246</v>
+        <f ca="1">IF($F13="","",$F13+90-TODAY())</f>
+        <v>-74</v>
       </c>
       <c r="N13" s="12">
         <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
@@ -14296,10 +14299,10 @@
         <v>99</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="T13" s="5" t="s">
         <v>76</v>

--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -235,20 +235,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -438,20 +424,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -647,20 +619,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -853,20 +811,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -1056,20 +1000,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -4454,7 +4384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO16"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4492,10 +4422,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>29</v>
       </c>
@@ -4616,11 +4545,8 @@
       <c r="AN1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>69</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>70</v>
       </c>
@@ -4730,11 +4656,8 @@
       <c r="AN2" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>85</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>86</v>
       </c>
@@ -4842,11 +4765,8 @@
       <c r="AN3" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>70</v>
       </c>
@@ -4956,11 +4876,8 @@
       <c r="AN4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>103</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>70</v>
       </c>
@@ -5068,11 +4985,8 @@
       <c r="AN5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>112</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -5182,11 +5096,8 @@
       <c r="AN6" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>115</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>70</v>
       </c>
@@ -5298,11 +5209,8 @@
       <c r="AN7" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>121</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>122</v>
       </c>
@@ -5414,11 +5322,8 @@
       <c r="AN8" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>132</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -5528,11 +5433,8 @@
       <c r="AN9" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>136</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -5640,11 +5542,8 @@
       <c r="AN10" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>142</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>565</v>
       </c>
@@ -5730,11 +5629,8 @@
       <c r="AN11" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>147</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>565</v>
       </c>
@@ -5820,13 +5716,10 @@
       <c r="AN12" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>150</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:AO12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AN12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="L2:L12">
     <cfRule type="expression" dxfId="99" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -5907,7 +5800,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AO32"/>
+  <dimension ref="A1:AN32"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5945,10 +5838,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>29</v>
       </c>
@@ -6069,11 +5961,8 @@
       <c r="AN1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>69</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>122</v>
       </c>
@@ -6189,11 +6078,8 @@
       <c r="AN2" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>160</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>70</v>
       </c>
@@ -6309,11 +6195,8 @@
       <c r="AN3" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>170</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>70</v>
       </c>
@@ -6423,11 +6306,8 @@
       <c r="AN4" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>176</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>70</v>
       </c>
@@ -6539,11 +6419,8 @@
       <c r="AN5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>181</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -6655,11 +6532,8 @@
       <c r="AN6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>186</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>86</v>
       </c>
@@ -6773,11 +6647,8 @@
       <c r="AN7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>191</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>565</v>
       </c>
@@ -6887,11 +6758,8 @@
       <c r="AN8" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>194</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -7003,11 +6871,8 @@
       <c r="AN9" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>198</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -7119,11 +6984,8 @@
       <c r="AN10" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>202</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>70</v>
       </c>
@@ -7235,11 +7097,8 @@
       <c r="AN11" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>203</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>122</v>
       </c>
@@ -7351,11 +7210,8 @@
       <c r="AN12" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>215</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3">
@@ -7461,11 +7317,8 @@
       <c r="AN13" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>224</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3">
@@ -7571,11 +7424,8 @@
       <c r="AN14" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>231</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3">
@@ -7683,11 +7533,8 @@
       <c r="AN15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>235</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="3">
@@ -7793,11 +7640,8 @@
       <c r="AN16" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>239</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="3">
@@ -7905,11 +7749,8 @@
       <c r="AN17" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>242</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3">
@@ -8017,11 +7858,8 @@
       <c r="AN18" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>244</v>
-      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3">
@@ -8129,11 +7967,8 @@
       <c r="AN19" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO19" s="5" t="s">
-        <v>246</v>
-      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="3">
@@ -8241,11 +8076,8 @@
       <c r="AN20" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO20" s="5" t="s">
-        <v>249</v>
-      </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="3">
@@ -8351,11 +8183,8 @@
       <c r="AN21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO21" s="5" t="s">
-        <v>252</v>
-      </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="3">
@@ -8463,11 +8292,8 @@
       <c r="AN22" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO22" s="5" t="s">
-        <v>254</v>
-      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="3">
@@ -8575,11 +8401,8 @@
       <c r="AN23" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO23" s="5" t="s">
-        <v>257</v>
-      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>565</v>
       </c>
@@ -8687,11 +8510,8 @@
       <c r="AN24" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO24" s="5" t="s">
-        <v>263</v>
-      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3">
@@ -8799,11 +8619,8 @@
       <c r="AN25" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO25" s="5" t="s">
-        <v>265</v>
-      </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="3">
@@ -8911,11 +8728,8 @@
       <c r="AN26" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO26" s="5" t="s">
-        <v>268</v>
-      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="3">
@@ -9023,11 +8837,8 @@
       <c r="AN27" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO27" s="5" t="s">
-        <v>275</v>
-      </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3">
@@ -9135,11 +8946,8 @@
       <c r="AN28" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO28" s="5" t="s">
-        <v>277</v>
-      </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="3">
@@ -9249,11 +9057,8 @@
       <c r="AN29" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO29" s="5" t="s">
-        <v>280</v>
-      </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="3">
@@ -9361,11 +9166,8 @@
       <c r="AN30" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO30" s="5" t="s">
-        <v>284</v>
-      </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>565</v>
       </c>
@@ -9457,11 +9259,8 @@
       <c r="AN31" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO31" s="5" t="s">
-        <v>290</v>
-      </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>565</v>
       </c>
@@ -9549,12 +9348,9 @@
       <c r="AN32" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AO32" s="5" t="s">
-        <v>294</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO32" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AN32" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <conditionalFormatting sqref="L2:L32">
     <cfRule type="expression" dxfId="79" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -9635,7 +9431,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AO7"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9673,10 +9469,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>29</v>
       </c>
@@ -9797,11 +9592,8 @@
       <c r="AN1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>69</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>122</v>
       </c>
@@ -9921,11 +9713,8 @@
       <c r="AN2" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>307</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>70</v>
       </c>
@@ -10045,11 +9834,8 @@
       <c r="AN3" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>316</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>565</v>
       </c>
@@ -10167,11 +9953,8 @@
       <c r="AN4" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>323</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>565</v>
       </c>
@@ -10287,11 +10070,8 @@
       <c r="AN5" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>327</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -10413,11 +10193,8 @@
       <c r="AN6" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>335</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>523</v>
       </c>
@@ -10519,12 +10296,9 @@
       <c r="AN7" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>340</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO7" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:AN7" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="L2:L7">
     <cfRule type="expression" dxfId="59" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -10605,7 +10379,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AO18"/>
+  <dimension ref="A1:AN18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10643,10 +10417,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>29</v>
       </c>
@@ -10767,11 +10540,8 @@
       <c r="AN1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>69</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>70</v>
       </c>
@@ -10883,11 +10653,8 @@
       <c r="AN2" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>347</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>70</v>
       </c>
@@ -10999,11 +10766,8 @@
       <c r="AN3" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>351</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>70</v>
       </c>
@@ -11113,11 +10877,8 @@
       <c r="AN4" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>352</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>86</v>
       </c>
@@ -11229,11 +10990,8 @@
       <c r="AN5" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>355</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -11347,11 +11105,8 @@
       <c r="AN6" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>359</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>70</v>
       </c>
@@ -11465,11 +11220,8 @@
       <c r="AN7" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>366</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>122</v>
       </c>
@@ -11581,11 +11333,8 @@
       <c r="AN8" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>371</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>122</v>
       </c>
@@ -11695,11 +11444,8 @@
       <c r="AN9" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>376</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -11813,11 +11559,8 @@
       <c r="AN10" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>389</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>122</v>
       </c>
@@ -11927,11 +11670,8 @@
       <c r="AN11" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>397</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>70</v>
       </c>
@@ -12045,11 +11785,8 @@
       <c r="AN12" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>402</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
@@ -12163,11 +11900,8 @@
       <c r="AN13" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>407</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>70</v>
       </c>
@@ -12283,11 +12017,8 @@
       <c r="AN14" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>413</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>70</v>
       </c>
@@ -12405,11 +12136,8 @@
       <c r="AN15" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>422</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>70</v>
       </c>
@@ -12519,11 +12247,8 @@
       <c r="AN16" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>426</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>565</v>
       </c>
@@ -12617,11 +12342,8 @@
       <c r="AN17" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>432</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>565</v>
       </c>
@@ -12713,12 +12435,9 @@
       <c r="AN18" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>435</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO18" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:AN18" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="L2:L18">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -12799,7 +12518,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO20"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -12837,10 +12556,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>29</v>
       </c>
@@ -12961,11 +12679,8 @@
       <c r="AN1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>69</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>122</v>
       </c>
@@ -13077,11 +12792,8 @@
       <c r="AN2" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>442</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>86</v>
       </c>
@@ -13195,11 +12907,8 @@
       <c r="AN3" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>446</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>86</v>
       </c>
@@ -13311,11 +13020,8 @@
       <c r="AN4" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>451</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>86</v>
       </c>
@@ -13423,11 +13129,8 @@
       <c r="AN5" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>456</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -13539,11 +13242,8 @@
       <c r="AN6" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>465</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>86</v>
       </c>
@@ -13659,11 +13359,8 @@
       <c r="AN7" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>470</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>86</v>
       </c>
@@ -13779,11 +13476,8 @@
       <c r="AN8" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>475</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -13893,11 +13587,8 @@
       <c r="AN9" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>480</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -14007,11 +13698,8 @@
       <c r="AN10" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>483</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>70</v>
       </c>
@@ -14121,11 +13809,8 @@
       <c r="AN11" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>486</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>70</v>
       </c>
@@ -14239,11 +13924,8 @@
       <c r="AN12" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>490</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
@@ -14353,11 +14035,8 @@
       <c r="AN13" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>493</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>70</v>
       </c>
@@ -14469,11 +14148,8 @@
       <c r="AN14" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>496</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>70</v>
       </c>
@@ -14583,11 +14259,8 @@
       <c r="AN15" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>499</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>565</v>
       </c>
@@ -14695,11 +14368,8 @@
       <c r="AN16" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>505</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>565</v>
       </c>
@@ -14809,11 +14479,8 @@
       <c r="AN17" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>508</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>70</v>
       </c>
@@ -14927,11 +14594,8 @@
       <c r="AN18" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>510</v>
-      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>565</v>
       </c>
@@ -15038,11 +14702,8 @@
       <c r="AN19" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO19" s="5" t="s">
-        <v>517</v>
-      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>565</v>
       </c>
@@ -15143,12 +14804,9 @@
       <c r="AN20" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="AO20" s="5" t="s">
-        <v>521</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO20" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:AN20" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <conditionalFormatting sqref="L2:L20">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>

--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -1008,7 +1008,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2122" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="586">
   <si>
     <t>2026-04 April - Specialty Claims</t>
   </si>
@@ -2745,6 +2745,27 @@
   </si>
   <si>
     <t xml:space="preserve">540 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84 claims with a date of service in 2026-04 April, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every specialty sheet is sorted by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: claims with five days or less left sit at the top of each sheet in red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order down the sheet, with the colour band each row gets, counted on 19 September 2026:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1 - Due in 5 days or less: 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2 - Due in 6-30 days: 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3 - Due in 31+ days: 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
 </sst>
 </file>
@@ -4218,7 +4239,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>1</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -4231,27 +4252,27 @@
     </row>
     <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>3</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>4</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>5</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>6</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>7</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -4361,7 +4382,7 @@
     </row>
     <row r="34" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>26</v>
+        <v>585</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="30" x14ac:dyDescent="0.25">

--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -1439,7 +1439,7 @@
     <t>777, 778</t>
   </si>
   <si>
-    <t>***Waiting for account to get activated again</t>
+    <t>Waiting for account to get activated again</t>
   </si>
   <si>
     <t>HF511715901</t>
@@ -1784,7 +1784,7 @@
     <t>788</t>
   </si>
   <si>
-    <t>***chat with ins to confirm covarage - ABN signed - charges per ins contract - PR non covered</t>
+    <t>chat with ins to confirm covarage - ABN signed - charges per ins contract - PR non covered</t>
   </si>
   <si>
     <t>HF331720981</t>
@@ -2594,28 +2594,28 @@
     <t>Uploaded MR - PIQ-90770826</t>
   </si>
   <si>
-    <t>***START A CHAT AND ASK FOR A PIQ REVIEW OR STATUS</t>
-  </si>
-  <si>
-    <t>***secondary - check cob on noridian, if nothing there, check with April - 1A95CU0TY97</t>
+    <t>START A CHAT AND ASK FOR A PIQ REVIEW OR STATUS</t>
+  </si>
+  <si>
+    <t>secondary - check cob on noridian, if nothing there, check with April - 1A95CU0TY97</t>
   </si>
   <si>
     <t>Added code 7, and resubmitted</t>
   </si>
   <si>
-    <t>***Send pending msm to Bri</t>
+    <t>Send pending msm to Bri</t>
   </si>
   <si>
     <t>Uploaded MR - PIQ-90772350</t>
   </si>
   <si>
-    <t xml:space="preserve">***DND 75710 This procedure or procedure/modifier combination is not compatible with another procedure or procedure/modifier combination provided on the same day according to the National Correct Coding Initiative or workers compensation state regulations/ fee schedule requirements - Adjusted balance for 36246 not included in the auth requested - 36248 add on requires payment for other cpt code - 99153 cant be billed on pos 24 </t>
+    <t xml:space="preserve">DND 75710 This procedure or procedure/modifier combination is not compatible with another procedure or procedure/modifier combination provided on the same day according to the National Correct Coding Initiative or workers compensation state regulations/ fee schedule requirements - Adjusted balance for 36246 not included in the auth requested - 36248 add on requires payment for other cpt code - 99153 cant be billed on pos 24 </t>
   </si>
   <si>
     <t>Adjusted balance for 75710, 75774, 36245</t>
   </si>
   <si>
-    <t xml:space="preserve">***DND 36248 due to exceeded MUE - DND 36245, 36246, and 75710 due to invalid dx </t>
+    <t xml:space="preserve">DND 36248 due to exceeded MUE - DND 36245, 36246, and 75710 due to invalid dx </t>
   </si>
   <si>
     <t xml:space="preserve">secondary - Added COB info, and resubmitted - Primary paid </t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">Requested auth on portal - Current Status: Not certified - NAR received was for 62330, which doesn't require authorization according to portal-Availity - DND no auth on file </t>
   </si>
   <si>
-    <t xml:space="preserve">***trying to get access to EOB with imperial </t>
-  </si>
-  <si>
-    <t>***no access</t>
+    <t xml:space="preserve">trying to get access to EOB with imperial </t>
+  </si>
+  <si>
+    <t>no access</t>
   </si>
   <si>
     <t xml:space="preserve">Uploaded MR - PIQ-91107053 as per insurance request </t>
@@ -2675,7 +2675,7 @@
     <t>Added mod XS to 93970, and resubmitted - Anthem Commercial Reimbursement Policy Number: C-23003 - secondary subject to MPPR rules</t>
   </si>
   <si>
-    <t xml:space="preserve">***Waiting for Bri's reply - Juan sent MR to me </t>
+    <t xml:space="preserve">Waiting for Bri's reply - Juan sent MR to me </t>
   </si>
   <si>
     <t>Adjusted balance - Acodes not included in auth/referral</t>
@@ -2702,7 +2702,7 @@
     <t>MBI updated - Resubmitted - DND Missing/incomplete/invalid patient identifier</t>
   </si>
   <si>
-    <t>***Shift to PT if I find same and similar on portal  - ABN signed - Another L0650 was dispensed back on 04/25/2022 - Supplier SONOSPINE ARIZONA LLC - DND L0650 M3 Equipment is the same or similar to equipment already being used</t>
+    <t>Shift to PT if I find same and similar on portal  - ABN signed - Another L0650 was dispensed back on 04/25/2022 - Supplier SONOSPINE ARIZONA LLC - DND L0650 M3 Equipment is the same or similar to equipment already being used</t>
   </si>
   <si>
     <t xml:space="preserve">Under Review</t>

--- a/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-04 April - Specialty Claims.xlsx
@@ -1008,7 +1008,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="587">
   <si>
     <t>2026-04 April - Specialty Claims</t>
   </si>
@@ -2766,6 +2766,9 @@
   </si>
   <si>
     <t xml:space="preserve">'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+  </si>
+  <si>
+    <t>93923 x1; 93970 x1</t>
   </si>
 </sst>
 </file>
@@ -13975,7 +13978,7 @@
         <v>74</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>472</v>
+        <v>586</v>
       </c>
       <c r="K13" s="3">
         <v>46283</v>
